--- a/model performance comparison/Ratio_Cfree_Cnominal/Huchthausen_data/Fischer model_ARE.xlsx
+++ b/model performance comparison/Ratio_Cfree_Cnominal/Huchthausen_data/Fischer model_ARE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Validation_Armitage\Validation_Hsu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\Validation_Armitage\Validation_Hsu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD626A8C-00D6-4447-B4F3-D4A1A4AC6141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB219DB8-1062-41C0-950C-466EB8101215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="9982" yWindow="2055" windowWidth="16321" windowHeight="10050" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model structure" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="97">
   <si>
     <t>Assumptions:</t>
   </si>
@@ -1061,18 +1061,6 @@
     <t>Lamotrigine</t>
   </si>
   <si>
-    <t>Venlafaxine</t>
-  </si>
-  <si>
-    <t>Metoprolol</t>
-  </si>
-  <si>
-    <t>Diphenhydramine</t>
-  </si>
-  <si>
-    <t>Propranolol</t>
-  </si>
-  <si>
     <t>2,4-Dichlorophenoxyacetic</t>
   </si>
   <si>
@@ -1095,18 +1083,6 @@
   </si>
   <si>
     <t>84057-84-1</t>
-  </si>
-  <si>
-    <t>99300-78-4</t>
-  </si>
-  <si>
-    <t>56392-17-7</t>
-  </si>
-  <si>
-    <t>147-24-0</t>
-  </si>
-  <si>
-    <t>318-98-9</t>
   </si>
   <si>
     <t>15307-79-6</t>
@@ -1136,19 +1112,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.000000000"/>
-    <numFmt numFmtId="166" formatCode="0.00000000000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="169" formatCode="0.00000_);[Red]\(0.00000\)"/>
-    <numFmt numFmtId="170" formatCode="0.000000_);[Red]\(0.000000\)"/>
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000000000"/>
+    <numFmt numFmtId="178" formatCode="0.00000000000"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="181" formatCode="0.00000_);[Red]\(0.00000\)"/>
+    <numFmt numFmtId="182" formatCode="0.000000_);[Red]\(0.000000\)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1265,13 +1241,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -1279,7 +1255,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1292,7 +1268,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1328,6 +1304,12 @@
       <sz val="11"/>
       <color theme="0" tint="-0.34998626667073579"/>
       <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1722,7 +1704,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1739,8 +1721,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1805,7 +1787,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1821,7 +1803,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1829,11 +1811,11 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1953,13 +1935,13 @@
     <xf numFmtId="2" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="20" fillId="8" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="21" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1975,9 +1957,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2050,6 +2029,143 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2138,12 +2254,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2171,140 +2281,21 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="1" xr:uid="{EAD913AB-B22E-45C0-B24F-41FAA7E034FC}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3480,7 +3471,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF297"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
@@ -3493,7 +3484,7 @@
     <col min="22" max="22" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" thickBot="1">
+    <row r="1" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -3527,35 +3518,35 @@
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
     </row>
-    <row r="2" spans="1:32" ht="18">
+    <row r="2" spans="1:32" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A2" s="7"/>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="118"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="117"/>
       <c r="I2" s="7"/>
-      <c r="J2" s="107" t="s">
+      <c r="J2" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="109"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="108"/>
       <c r="P2" s="7"/>
-      <c r="Q2" s="107" t="s">
+      <c r="Q2" s="106" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="109"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="107"/>
+      <c r="T2" s="107"/>
+      <c r="U2" s="107"/>
+      <c r="V2" s="108"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
@@ -3567,7 +3558,7 @@
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" s="7"/>
       <c r="B3" s="25" t="s">
         <v>0</v>
@@ -3581,19 +3572,19 @@
       <c r="G3" s="26"/>
       <c r="H3" s="27"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="112"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="111"/>
       <c r="P3" s="7"/>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="112"/>
+      <c r="Q3" s="109"/>
+      <c r="R3" s="110"/>
+      <c r="S3" s="110"/>
+      <c r="T3" s="110"/>
+      <c r="U3" s="110"/>
+      <c r="V3" s="111"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -3605,7 +3596,7 @@
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
     </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7"/>
       <c r="B4" s="28"/>
       <c r="C4" s="29" t="s">
@@ -3617,19 +3608,19 @@
       <c r="G4" s="29"/>
       <c r="H4" s="31"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="115"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="113"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
+      <c r="N4" s="113"/>
+      <c r="O4" s="114"/>
       <c r="P4" s="7"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="115"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113"/>
+      <c r="V4" s="114"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
@@ -3641,7 +3632,7 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
     </row>
-    <row r="5" spans="1:32" ht="15" customHeight="1">
+    <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="20"/>
       <c r="C5" s="1"/>
@@ -3675,7 +3666,7 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
     </row>
-    <row r="6" spans="1:32" ht="31.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:32" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="7"/>
       <c r="B6" s="22"/>
       <c r="C6" s="23"/>
@@ -3715,7 +3706,7 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" s="7"/>
       <c r="B7" s="12"/>
       <c r="C7" s="7"/>
@@ -3755,7 +3746,7 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
     </row>
-    <row r="8" spans="1:32" ht="15.75" thickBot="1">
+    <row r="8" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="7"/>
       <c r="B8" s="12"/>
       <c r="C8" s="7"/>
@@ -3795,7 +3786,7 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
       <c r="B9" s="12"/>
       <c r="C9" s="7"/>
@@ -3835,7 +3826,7 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
     </row>
-    <row r="10" spans="1:32" ht="15.75" thickBot="1">
+    <row r="10" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
       <c r="B10" s="12"/>
       <c r="C10" s="7"/>
@@ -3875,7 +3866,7 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
       <c r="B11" s="12"/>
       <c r="C11" s="7"/>
@@ -3915,7 +3906,7 @@
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
       <c r="B12" s="12"/>
       <c r="C12" s="7"/>
@@ -3955,7 +3946,7 @@
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
     </row>
-    <row r="13" spans="1:32" ht="15.75" thickBot="1">
+    <row r="13" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="7"/>
       <c r="B13" s="12"/>
       <c r="C13" s="7"/>
@@ -3989,7 +3980,7 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
     </row>
-    <row r="14" spans="1:32" ht="33" customHeight="1" thickBot="1">
+    <row r="14" spans="1:32" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="7"/>
       <c r="B14" s="12"/>
       <c r="C14" s="7"/>
@@ -4031,7 +4022,7 @@
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
       <c r="B15" s="12"/>
       <c r="C15" s="7"/>
@@ -4073,7 +4064,7 @@
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
     </row>
-    <row r="16" spans="1:32" ht="15.75" thickBot="1">
+    <row r="16" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="7"/>
       <c r="B16" s="12"/>
       <c r="C16" s="7"/>
@@ -4115,7 +4106,7 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A17" s="7"/>
       <c r="B17" s="12"/>
       <c r="C17" s="7"/>
@@ -4157,7 +4148,7 @@
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A18" s="7"/>
       <c r="B18" s="12"/>
       <c r="C18" s="7"/>
@@ -4199,7 +4190,7 @@
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
     </row>
-    <row r="19" spans="1:32" ht="15.75" thickBot="1">
+    <row r="19" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="7"/>
       <c r="B19" s="12"/>
       <c r="C19" s="7"/>
@@ -4241,7 +4232,7 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
     </row>
-    <row r="20" spans="1:32" ht="15.75" thickBot="1">
+    <row r="20" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="7"/>
       <c r="B20" s="12"/>
       <c r="C20" s="7"/>
@@ -4275,7 +4266,7 @@
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
     </row>
-    <row r="21" spans="1:32">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A21" s="7"/>
       <c r="B21" s="12"/>
       <c r="C21" s="7"/>
@@ -4309,7 +4300,7 @@
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
     </row>
-    <row r="22" spans="1:32" ht="15.75" thickBot="1">
+    <row r="22" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="7"/>
       <c r="B22" s="12"/>
       <c r="C22" s="7"/>
@@ -4343,7 +4334,7 @@
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A23" s="7"/>
       <c r="B23" s="12"/>
       <c r="C23" s="7"/>
@@ -4387,7 +4378,7 @@
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
     </row>
-    <row r="24" spans="1:32" ht="15.75" thickBot="1">
+    <row r="24" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="7"/>
       <c r="B24" s="13"/>
       <c r="C24" s="24"/>
@@ -4433,7 +4424,7 @@
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
     </row>
-    <row r="25" spans="1:32" ht="15.75" thickBot="1">
+    <row r="25" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -4470,7 +4461,7 @@
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -4504,7 +4495,7 @@
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
     </row>
-    <row r="27" spans="1:32" ht="15.75" thickBot="1">
+    <row r="27" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -4538,7 +4529,7 @@
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -4572,7 +4563,7 @@
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -4605,7 +4596,7 @@
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -4639,7 +4630,7 @@
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
     </row>
-    <row r="31" spans="1:32" ht="15.75" thickBot="1">
+    <row r="31" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -4673,7 +4664,7 @@
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -4706,7 +4697,7 @@
       <c r="AE32" s="7"/>
       <c r="AF32" s="7"/>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -4737,7 +4728,7 @@
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -4769,7 +4760,7 @@
       <c r="AE34" s="7"/>
       <c r="AF34" s="7"/>
     </row>
-    <row r="35" spans="1:32" ht="15.75" thickBot="1">
+    <row r="35" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -4803,7 +4794,7 @@
       <c r="AE35" s="7"/>
       <c r="AF35" s="7"/>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -4835,7 +4826,7 @@
       <c r="AE36" s="7"/>
       <c r="AF36" s="7"/>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -4868,7 +4859,7 @@
       <c r="AE37" s="7"/>
       <c r="AF37" s="7"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -4902,7 +4893,7 @@
       <c r="AE38" s="7"/>
       <c r="AF38" s="7"/>
     </row>
-    <row r="39" spans="1:32" ht="15.75" thickBot="1">
+    <row r="39" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -4936,7 +4927,7 @@
       <c r="AE39" s="7"/>
       <c r="AF39" s="7"/>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -4970,7 +4961,7 @@
       <c r="AE40" s="7"/>
       <c r="AF40" s="7"/>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -5004,7 +4995,7 @@
       <c r="AE41" s="7"/>
       <c r="AF41" s="7"/>
     </row>
-    <row r="42" spans="1:32" ht="15.75" thickBot="1">
+    <row r="42" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -5038,7 +5029,7 @@
       <c r="AE42" s="7"/>
       <c r="AF42" s="7"/>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -5072,7 +5063,7 @@
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -5106,7 +5097,7 @@
       <c r="AE44" s="7"/>
       <c r="AF44" s="7"/>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -5140,7 +5131,7 @@
       <c r="AE45" s="7"/>
       <c r="AF45" s="7"/>
     </row>
-    <row r="46" spans="1:32" ht="15.75" thickBot="1">
+    <row r="46" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -5174,7 +5165,7 @@
       <c r="AE46" s="7"/>
       <c r="AF46" s="7"/>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -5208,7 +5199,7 @@
       <c r="AE47" s="7"/>
       <c r="AF47" s="7"/>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -5242,7 +5233,7 @@
       <c r="AE48" s="7"/>
       <c r="AF48" s="7"/>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -5276,7 +5267,7 @@
       <c r="AE49" s="7"/>
       <c r="AF49" s="7"/>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -5310,7 +5301,7 @@
       <c r="AE50" s="7"/>
       <c r="AF50" s="7"/>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -5344,7 +5335,7 @@
       <c r="AE51" s="7"/>
       <c r="AF51" s="7"/>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -5378,7 +5369,7 @@
       <c r="AE52" s="7"/>
       <c r="AF52" s="7"/>
     </row>
-    <row r="53" spans="1:32">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -5412,7 +5403,7 @@
       <c r="AE53" s="7"/>
       <c r="AF53" s="7"/>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -5446,7 +5437,7 @@
       <c r="AE54" s="7"/>
       <c r="AF54" s="7"/>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -5480,7 +5471,7 @@
       <c r="AE55" s="7"/>
       <c r="AF55" s="7"/>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -5514,7 +5505,7 @@
       <c r="AE56" s="7"/>
       <c r="AF56" s="7"/>
     </row>
-    <row r="57" spans="1:32">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -5548,7 +5539,7 @@
       <c r="AE57" s="7"/>
       <c r="AF57" s="7"/>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -5582,7 +5573,7 @@
       <c r="AE58" s="7"/>
       <c r="AF58" s="7"/>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -5616,7 +5607,7 @@
       <c r="AE59" s="7"/>
       <c r="AF59" s="7"/>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -5650,7 +5641,7 @@
       <c r="AE60" s="7"/>
       <c r="AF60" s="7"/>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -5684,7 +5675,7 @@
       <c r="AE61" s="7"/>
       <c r="AF61" s="7"/>
     </row>
-    <row r="62" spans="1:32">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -5718,7 +5709,7 @@
       <c r="AE62" s="7"/>
       <c r="AF62" s="7"/>
     </row>
-    <row r="63" spans="1:32">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -5752,7 +5743,7 @@
       <c r="AE63" s="7"/>
       <c r="AF63" s="7"/>
     </row>
-    <row r="64" spans="1:32">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -5786,7 +5777,7 @@
       <c r="AE64" s="7"/>
       <c r="AF64" s="7"/>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -5820,7 +5811,7 @@
       <c r="AE65" s="7"/>
       <c r="AF65" s="7"/>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -5854,7 +5845,7 @@
       <c r="AE66" s="7"/>
       <c r="AF66" s="7"/>
     </row>
-    <row r="67" spans="1:32">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -5888,7 +5879,7 @@
       <c r="AE67" s="7"/>
       <c r="AF67" s="7"/>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -5922,7 +5913,7 @@
       <c r="AE68" s="7"/>
       <c r="AF68" s="7"/>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -5956,7 +5947,7 @@
       <c r="AE69" s="7"/>
       <c r="AF69" s="7"/>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -5990,7 +5981,7 @@
       <c r="AE70" s="7"/>
       <c r="AF70" s="7"/>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -6024,7 +6015,7 @@
       <c r="AE71" s="7"/>
       <c r="AF71" s="7"/>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -6058,7 +6049,7 @@
       <c r="AE72" s="7"/>
       <c r="AF72" s="7"/>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -6092,7 +6083,7 @@
       <c r="AE73" s="7"/>
       <c r="AF73" s="7"/>
     </row>
-    <row r="74" spans="1:32">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -6126,7 +6117,7 @@
       <c r="AE74" s="7"/>
       <c r="AF74" s="7"/>
     </row>
-    <row r="75" spans="1:32">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -6160,7 +6151,7 @@
       <c r="AE75" s="7"/>
       <c r="AF75" s="7"/>
     </row>
-    <row r="76" spans="1:32">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -6194,7 +6185,7 @@
       <c r="AE76" s="7"/>
       <c r="AF76" s="7"/>
     </row>
-    <row r="77" spans="1:32">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -6228,7 +6219,7 @@
       <c r="AE77" s="7"/>
       <c r="AF77" s="7"/>
     </row>
-    <row r="78" spans="1:32">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -6262,7 +6253,7 @@
       <c r="AE78" s="7"/>
       <c r="AF78" s="7"/>
     </row>
-    <row r="79" spans="1:32">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -6296,7 +6287,7 @@
       <c r="AE79" s="7"/>
       <c r="AF79" s="7"/>
     </row>
-    <row r="80" spans="1:32">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -6330,7 +6321,7 @@
       <c r="AE80" s="7"/>
       <c r="AF80" s="7"/>
     </row>
-    <row r="81" spans="1:32">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -6364,7 +6355,7 @@
       <c r="AE81" s="7"/>
       <c r="AF81" s="7"/>
     </row>
-    <row r="82" spans="1:32">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -6398,7 +6389,7 @@
       <c r="AE82" s="7"/>
       <c r="AF82" s="7"/>
     </row>
-    <row r="83" spans="1:32">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -6432,7 +6423,7 @@
       <c r="AE83" s="7"/>
       <c r="AF83" s="7"/>
     </row>
-    <row r="84" spans="1:32">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -6466,7 +6457,7 @@
       <c r="AE84" s="7"/>
       <c r="AF84" s="7"/>
     </row>
-    <row r="85" spans="1:32">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -6500,7 +6491,7 @@
       <c r="AE85" s="7"/>
       <c r="AF85" s="7"/>
     </row>
-    <row r="86" spans="1:32">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -6534,7 +6525,7 @@
       <c r="AE86" s="7"/>
       <c r="AF86" s="7"/>
     </row>
-    <row r="87" spans="1:32">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -6568,7 +6559,7 @@
       <c r="AE87" s="7"/>
       <c r="AF87" s="7"/>
     </row>
-    <row r="88" spans="1:32">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -6602,7 +6593,7 @@
       <c r="AE88" s="7"/>
       <c r="AF88" s="7"/>
     </row>
-    <row r="89" spans="1:32">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -6636,7 +6627,7 @@
       <c r="AE89" s="7"/>
       <c r="AF89" s="7"/>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -6670,7 +6661,7 @@
       <c r="AE90" s="7"/>
       <c r="AF90" s="7"/>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -6704,7 +6695,7 @@
       <c r="AE91" s="7"/>
       <c r="AF91" s="7"/>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -6738,7 +6729,7 @@
       <c r="AE92" s="7"/>
       <c r="AF92" s="7"/>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -6772,7 +6763,7 @@
       <c r="AE93" s="7"/>
       <c r="AF93" s="7"/>
     </row>
-    <row r="94" spans="1:32">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -6806,7 +6797,7 @@
       <c r="AE94" s="7"/>
       <c r="AF94" s="7"/>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -6840,7 +6831,7 @@
       <c r="AE95" s="7"/>
       <c r="AF95" s="7"/>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -6874,7 +6865,7 @@
       <c r="AE96" s="7"/>
       <c r="AF96" s="7"/>
     </row>
-    <row r="97" spans="1:32">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -6908,7 +6899,7 @@
       <c r="AE97" s="7"/>
       <c r="AF97" s="7"/>
     </row>
-    <row r="98" spans="1:32">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -6942,7 +6933,7 @@
       <c r="AE98" s="7"/>
       <c r="AF98" s="7"/>
     </row>
-    <row r="99" spans="1:32">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -6976,7 +6967,7 @@
       <c r="AE99" s="7"/>
       <c r="AF99" s="7"/>
     </row>
-    <row r="100" spans="1:32">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -7010,7 +7001,7 @@
       <c r="AE100" s="7"/>
       <c r="AF100" s="7"/>
     </row>
-    <row r="101" spans="1:32">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -7044,7 +7035,7 @@
       <c r="AE101" s="7"/>
       <c r="AF101" s="7"/>
     </row>
-    <row r="102" spans="1:32">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -7078,7 +7069,7 @@
       <c r="AE102" s="7"/>
       <c r="AF102" s="7"/>
     </row>
-    <row r="103" spans="1:32">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -7112,7 +7103,7 @@
       <c r="AE103" s="7"/>
       <c r="AF103" s="7"/>
     </row>
-    <row r="104" spans="1:32">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -7146,7 +7137,7 @@
       <c r="AE104" s="7"/>
       <c r="AF104" s="7"/>
     </row>
-    <row r="105" spans="1:32">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -7180,7 +7171,7 @@
       <c r="AE105" s="7"/>
       <c r="AF105" s="7"/>
     </row>
-    <row r="106" spans="1:32">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -7214,7 +7205,7 @@
       <c r="AE106" s="7"/>
       <c r="AF106" s="7"/>
     </row>
-    <row r="107" spans="1:32">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -7248,7 +7239,7 @@
       <c r="AE107" s="7"/>
       <c r="AF107" s="7"/>
     </row>
-    <row r="108" spans="1:32">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -7282,7 +7273,7 @@
       <c r="AE108" s="7"/>
       <c r="AF108" s="7"/>
     </row>
-    <row r="109" spans="1:32">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -7316,7 +7307,7 @@
       <c r="AE109" s="7"/>
       <c r="AF109" s="7"/>
     </row>
-    <row r="110" spans="1:32">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -7350,7 +7341,7 @@
       <c r="AE110" s="7"/>
       <c r="AF110" s="7"/>
     </row>
-    <row r="111" spans="1:32">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -7384,7 +7375,7 @@
       <c r="AE111" s="7"/>
       <c r="AF111" s="7"/>
     </row>
-    <row r="112" spans="1:32">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -7418,7 +7409,7 @@
       <c r="AE112" s="7"/>
       <c r="AF112" s="7"/>
     </row>
-    <row r="113" spans="1:32">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -7452,7 +7443,7 @@
       <c r="AE113" s="7"/>
       <c r="AF113" s="7"/>
     </row>
-    <row r="114" spans="1:32">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -7486,7 +7477,7 @@
       <c r="AE114" s="7"/>
       <c r="AF114" s="7"/>
     </row>
-    <row r="115" spans="1:32">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -7520,7 +7511,7 @@
       <c r="AE115" s="7"/>
       <c r="AF115" s="7"/>
     </row>
-    <row r="116" spans="1:32">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -7554,7 +7545,7 @@
       <c r="AE116" s="7"/>
       <c r="AF116" s="7"/>
     </row>
-    <row r="117" spans="1:32">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -7588,7 +7579,7 @@
       <c r="AE117" s="7"/>
       <c r="AF117" s="7"/>
     </row>
-    <row r="118" spans="1:32">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -7622,7 +7613,7 @@
       <c r="AE118" s="7"/>
       <c r="AF118" s="7"/>
     </row>
-    <row r="119" spans="1:32">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -7656,7 +7647,7 @@
       <c r="AE119" s="7"/>
       <c r="AF119" s="7"/>
     </row>
-    <row r="120" spans="1:32">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -7690,7 +7681,7 @@
       <c r="AE120" s="7"/>
       <c r="AF120" s="7"/>
     </row>
-    <row r="121" spans="1:32">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -7724,7 +7715,7 @@
       <c r="AE121" s="7"/>
       <c r="AF121" s="7"/>
     </row>
-    <row r="122" spans="1:32">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
@@ -7758,7 +7749,7 @@
       <c r="AE122" s="7"/>
       <c r="AF122" s="7"/>
     </row>
-    <row r="123" spans="1:32">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
@@ -7792,7 +7783,7 @@
       <c r="AE123" s="7"/>
       <c r="AF123" s="7"/>
     </row>
-    <row r="124" spans="1:32">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -7826,7 +7817,7 @@
       <c r="AE124" s="7"/>
       <c r="AF124" s="7"/>
     </row>
-    <row r="125" spans="1:32">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -7860,7 +7851,7 @@
       <c r="AE125" s="7"/>
       <c r="AF125" s="7"/>
     </row>
-    <row r="126" spans="1:32">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -7894,7 +7885,7 @@
       <c r="AE126" s="7"/>
       <c r="AF126" s="7"/>
     </row>
-    <row r="127" spans="1:32">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -7928,7 +7919,7 @@
       <c r="AE127" s="7"/>
       <c r="AF127" s="7"/>
     </row>
-    <row r="128" spans="1:32">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -7962,7 +7953,7 @@
       <c r="AE128" s="7"/>
       <c r="AF128" s="7"/>
     </row>
-    <row r="129" spans="1:32">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -7996,7 +7987,7 @@
       <c r="AE129" s="7"/>
       <c r="AF129" s="7"/>
     </row>
-    <row r="130" spans="1:32">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -8030,7 +8021,7 @@
       <c r="AE130" s="7"/>
       <c r="AF130" s="7"/>
     </row>
-    <row r="131" spans="1:32">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -8064,7 +8055,7 @@
       <c r="AE131" s="7"/>
       <c r="AF131" s="7"/>
     </row>
-    <row r="132" spans="1:32">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -8098,7 +8089,7 @@
       <c r="AE132" s="7"/>
       <c r="AF132" s="7"/>
     </row>
-    <row r="133" spans="1:32">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -8132,7 +8123,7 @@
       <c r="AE133" s="7"/>
       <c r="AF133" s="7"/>
     </row>
-    <row r="134" spans="1:32">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -8166,7 +8157,7 @@
       <c r="AE134" s="7"/>
       <c r="AF134" s="7"/>
     </row>
-    <row r="135" spans="1:32">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -8200,7 +8191,7 @@
       <c r="AE135" s="7"/>
       <c r="AF135" s="7"/>
     </row>
-    <row r="136" spans="1:32">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -8234,7 +8225,7 @@
       <c r="AE136" s="7"/>
       <c r="AF136" s="7"/>
     </row>
-    <row r="137" spans="1:32">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -8268,7 +8259,7 @@
       <c r="AE137" s="7"/>
       <c r="AF137" s="7"/>
     </row>
-    <row r="138" spans="1:32">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -8302,7 +8293,7 @@
       <c r="AE138" s="7"/>
       <c r="AF138" s="7"/>
     </row>
-    <row r="139" spans="1:32">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -8336,7 +8327,7 @@
       <c r="AE139" s="7"/>
       <c r="AF139" s="7"/>
     </row>
-    <row r="140" spans="1:32">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
@@ -8370,7 +8361,7 @@
       <c r="AE140" s="7"/>
       <c r="AF140" s="7"/>
     </row>
-    <row r="141" spans="1:32">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
@@ -8404,7 +8395,7 @@
       <c r="AE141" s="7"/>
       <c r="AF141" s="7"/>
     </row>
-    <row r="142" spans="1:32">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
@@ -8438,7 +8429,7 @@
       <c r="AE142" s="7"/>
       <c r="AF142" s="7"/>
     </row>
-    <row r="143" spans="1:32">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
@@ -8472,7 +8463,7 @@
       <c r="AE143" s="7"/>
       <c r="AF143" s="7"/>
     </row>
-    <row r="144" spans="1:32">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
@@ -8506,7 +8497,7 @@
       <c r="AE144" s="7"/>
       <c r="AF144" s="7"/>
     </row>
-    <row r="145" spans="1:32">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
@@ -8540,7 +8531,7 @@
       <c r="AE145" s="7"/>
       <c r="AF145" s="7"/>
     </row>
-    <row r="146" spans="1:32">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
@@ -8574,7 +8565,7 @@
       <c r="AE146" s="7"/>
       <c r="AF146" s="7"/>
     </row>
-    <row r="147" spans="1:32">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
@@ -8608,7 +8599,7 @@
       <c r="AE147" s="7"/>
       <c r="AF147" s="7"/>
     </row>
-    <row r="148" spans="1:32">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
@@ -8642,7 +8633,7 @@
       <c r="AE148" s="7"/>
       <c r="AF148" s="7"/>
     </row>
-    <row r="149" spans="1:32">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
@@ -8676,7 +8667,7 @@
       <c r="AE149" s="7"/>
       <c r="AF149" s="7"/>
     </row>
-    <row r="150" spans="1:32">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
@@ -8710,7 +8701,7 @@
       <c r="AE150" s="7"/>
       <c r="AF150" s="7"/>
     </row>
-    <row r="151" spans="1:32">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
@@ -8744,7 +8735,7 @@
       <c r="AE151" s="7"/>
       <c r="AF151" s="7"/>
     </row>
-    <row r="152" spans="1:32">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
@@ -8778,7 +8769,7 @@
       <c r="AE152" s="7"/>
       <c r="AF152" s="7"/>
     </row>
-    <row r="153" spans="1:32">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
@@ -8812,7 +8803,7 @@
       <c r="AE153" s="7"/>
       <c r="AF153" s="7"/>
     </row>
-    <row r="154" spans="1:32">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
@@ -8846,7 +8837,7 @@
       <c r="AE154" s="7"/>
       <c r="AF154" s="7"/>
     </row>
-    <row r="155" spans="1:32">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
@@ -8880,7 +8871,7 @@
       <c r="AE155" s="7"/>
       <c r="AF155" s="7"/>
     </row>
-    <row r="156" spans="1:32">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
@@ -8914,7 +8905,7 @@
       <c r="AE156" s="7"/>
       <c r="AF156" s="7"/>
     </row>
-    <row r="157" spans="1:32">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
@@ -8948,7 +8939,7 @@
       <c r="AE157" s="7"/>
       <c r="AF157" s="7"/>
     </row>
-    <row r="158" spans="1:32">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
@@ -8982,7 +8973,7 @@
       <c r="AE158" s="7"/>
       <c r="AF158" s="7"/>
     </row>
-    <row r="159" spans="1:32">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
@@ -9016,7 +9007,7 @@
       <c r="AE159" s="7"/>
       <c r="AF159" s="7"/>
     </row>
-    <row r="160" spans="1:32">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
@@ -9050,7 +9041,7 @@
       <c r="AE160" s="7"/>
       <c r="AF160" s="7"/>
     </row>
-    <row r="161" spans="1:32">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
@@ -9084,7 +9075,7 @@
       <c r="AE161" s="7"/>
       <c r="AF161" s="7"/>
     </row>
-    <row r="162" spans="1:32">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
@@ -9118,7 +9109,7 @@
       <c r="AE162" s="7"/>
       <c r="AF162" s="7"/>
     </row>
-    <row r="163" spans="1:32">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
@@ -9152,7 +9143,7 @@
       <c r="AE163" s="7"/>
       <c r="AF163" s="7"/>
     </row>
-    <row r="164" spans="1:32">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
@@ -9186,7 +9177,7 @@
       <c r="AE164" s="7"/>
       <c r="AF164" s="7"/>
     </row>
-    <row r="165" spans="1:32">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
@@ -9220,7 +9211,7 @@
       <c r="AE165" s="7"/>
       <c r="AF165" s="7"/>
     </row>
-    <row r="166" spans="1:32">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
@@ -9254,7 +9245,7 @@
       <c r="AE166" s="7"/>
       <c r="AF166" s="7"/>
     </row>
-    <row r="167" spans="1:32">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
@@ -9288,7 +9279,7 @@
       <c r="AE167" s="7"/>
       <c r="AF167" s="7"/>
     </row>
-    <row r="168" spans="1:32">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
@@ -9322,7 +9313,7 @@
       <c r="AE168" s="7"/>
       <c r="AF168" s="7"/>
     </row>
-    <row r="169" spans="1:32">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
@@ -9356,7 +9347,7 @@
       <c r="AE169" s="7"/>
       <c r="AF169" s="7"/>
     </row>
-    <row r="170" spans="1:32">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
@@ -9390,7 +9381,7 @@
       <c r="AE170" s="7"/>
       <c r="AF170" s="7"/>
     </row>
-    <row r="171" spans="1:32">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
       <c r="C171" s="7"/>
@@ -9424,7 +9415,7 @@
       <c r="AE171" s="7"/>
       <c r="AF171" s="7"/>
     </row>
-    <row r="172" spans="1:32">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="7"/>
@@ -9458,7 +9449,7 @@
       <c r="AE172" s="7"/>
       <c r="AF172" s="7"/>
     </row>
-    <row r="173" spans="1:32">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
       <c r="C173" s="7"/>
@@ -9492,7 +9483,7 @@
       <c r="AE173" s="7"/>
       <c r="AF173" s="7"/>
     </row>
-    <row r="174" spans="1:32">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="7"/>
@@ -9526,7 +9517,7 @@
       <c r="AE174" s="7"/>
       <c r="AF174" s="7"/>
     </row>
-    <row r="175" spans="1:32">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
       <c r="C175" s="7"/>
@@ -9560,7 +9551,7 @@
       <c r="AE175" s="7"/>
       <c r="AF175" s="7"/>
     </row>
-    <row r="176" spans="1:32">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="7"/>
@@ -9594,7 +9585,7 @@
       <c r="AE176" s="7"/>
       <c r="AF176" s="7"/>
     </row>
-    <row r="177" spans="1:32">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="7"/>
@@ -9628,7 +9619,7 @@
       <c r="AE177" s="7"/>
       <c r="AF177" s="7"/>
     </row>
-    <row r="178" spans="1:32">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="7"/>
@@ -9662,7 +9653,7 @@
       <c r="AE178" s="7"/>
       <c r="AF178" s="7"/>
     </row>
-    <row r="179" spans="1:32">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="7"/>
@@ -9696,7 +9687,7 @@
       <c r="AE179" s="7"/>
       <c r="AF179" s="7"/>
     </row>
-    <row r="180" spans="1:32">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="7"/>
@@ -9730,7 +9721,7 @@
       <c r="AE180" s="7"/>
       <c r="AF180" s="7"/>
     </row>
-    <row r="181" spans="1:32">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="7"/>
@@ -9764,7 +9755,7 @@
       <c r="AE181" s="7"/>
       <c r="AF181" s="7"/>
     </row>
-    <row r="182" spans="1:32">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="7"/>
@@ -9798,7 +9789,7 @@
       <c r="AE182" s="7"/>
       <c r="AF182" s="7"/>
     </row>
-    <row r="183" spans="1:32">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
       <c r="C183" s="7"/>
@@ -9832,7 +9823,7 @@
       <c r="AE183" s="7"/>
       <c r="AF183" s="7"/>
     </row>
-    <row r="184" spans="1:32">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="7"/>
@@ -9866,7 +9857,7 @@
       <c r="AE184" s="7"/>
       <c r="AF184" s="7"/>
     </row>
-    <row r="185" spans="1:32">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
       <c r="C185" s="7"/>
@@ -9900,7 +9891,7 @@
       <c r="AE185" s="7"/>
       <c r="AF185" s="7"/>
     </row>
-    <row r="186" spans="1:32">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="7"/>
@@ -9934,7 +9925,7 @@
       <c r="AE186" s="7"/>
       <c r="AF186" s="7"/>
     </row>
-    <row r="187" spans="1:32">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
       <c r="C187" s="7"/>
@@ -9968,7 +9959,7 @@
       <c r="AE187" s="7"/>
       <c r="AF187" s="7"/>
     </row>
-    <row r="188" spans="1:32">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
       <c r="C188" s="7"/>
@@ -10002,7 +9993,7 @@
       <c r="AE188" s="7"/>
       <c r="AF188" s="7"/>
     </row>
-    <row r="189" spans="1:32">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
       <c r="C189" s="7"/>
@@ -10036,7 +10027,7 @@
       <c r="AE189" s="7"/>
       <c r="AF189" s="7"/>
     </row>
-    <row r="190" spans="1:32">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
       <c r="C190" s="7"/>
@@ -10070,7 +10061,7 @@
       <c r="AE190" s="7"/>
       <c r="AF190" s="7"/>
     </row>
-    <row r="191" spans="1:32">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
       <c r="C191" s="7"/>
@@ -10104,7 +10095,7 @@
       <c r="AE191" s="7"/>
       <c r="AF191" s="7"/>
     </row>
-    <row r="192" spans="1:32">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
       <c r="C192" s="7"/>
@@ -10138,7 +10129,7 @@
       <c r="AE192" s="7"/>
       <c r="AF192" s="7"/>
     </row>
-    <row r="193" spans="1:32">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
       <c r="C193" s="7"/>
@@ -10172,7 +10163,7 @@
       <c r="AE193" s="7"/>
       <c r="AF193" s="7"/>
     </row>
-    <row r="194" spans="1:32">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
@@ -10206,7 +10197,7 @@
       <c r="AE194" s="7"/>
       <c r="AF194" s="7"/>
     </row>
-    <row r="195" spans="1:32">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
@@ -10240,7 +10231,7 @@
       <c r="AE195" s="7"/>
       <c r="AF195" s="7"/>
     </row>
-    <row r="196" spans="1:32">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
       <c r="C196" s="7"/>
@@ -10274,7 +10265,7 @@
       <c r="AE196" s="7"/>
       <c r="AF196" s="7"/>
     </row>
-    <row r="197" spans="1:32">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
       <c r="C197" s="7"/>
@@ -10308,7 +10299,7 @@
       <c r="AE197" s="7"/>
       <c r="AF197" s="7"/>
     </row>
-    <row r="198" spans="1:32">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
       <c r="C198" s="7"/>
@@ -10342,7 +10333,7 @@
       <c r="AE198" s="7"/>
       <c r="AF198" s="7"/>
     </row>
-    <row r="199" spans="1:32">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
       <c r="C199" s="7"/>
@@ -10376,7 +10367,7 @@
       <c r="AE199" s="7"/>
       <c r="AF199" s="7"/>
     </row>
-    <row r="200" spans="1:32">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
       <c r="C200" s="7"/>
@@ -10410,7 +10401,7 @@
       <c r="AE200" s="7"/>
       <c r="AF200" s="7"/>
     </row>
-    <row r="201" spans="1:32">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
       <c r="C201" s="7"/>
@@ -10444,7 +10435,7 @@
       <c r="AE201" s="7"/>
       <c r="AF201" s="7"/>
     </row>
-    <row r="202" spans="1:32">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
       <c r="C202" s="7"/>
@@ -10478,7 +10469,7 @@
       <c r="AE202" s="7"/>
       <c r="AF202" s="7"/>
     </row>
-    <row r="203" spans="1:32">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
       <c r="C203" s="7"/>
@@ -10512,7 +10503,7 @@
       <c r="AE203" s="7"/>
       <c r="AF203" s="7"/>
     </row>
-    <row r="204" spans="1:32">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
       <c r="C204" s="7"/>
@@ -10546,7 +10537,7 @@
       <c r="AE204" s="7"/>
       <c r="AF204" s="7"/>
     </row>
-    <row r="205" spans="1:32">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
       <c r="C205" s="7"/>
@@ -10580,7 +10571,7 @@
       <c r="AE205" s="7"/>
       <c r="AF205" s="7"/>
     </row>
-    <row r="206" spans="1:32">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
       <c r="C206" s="7"/>
@@ -10614,7 +10605,7 @@
       <c r="AE206" s="7"/>
       <c r="AF206" s="7"/>
     </row>
-    <row r="207" spans="1:32">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A207" s="7"/>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -10648,7 +10639,7 @@
       <c r="AE207" s="7"/>
       <c r="AF207" s="7"/>
     </row>
-    <row r="208" spans="1:32">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A208" s="7"/>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -10682,7 +10673,7 @@
       <c r="AE208" s="7"/>
       <c r="AF208" s="7"/>
     </row>
-    <row r="209" spans="1:32">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A209" s="7"/>
       <c r="B209" s="7"/>
       <c r="C209" s="7"/>
@@ -10716,7 +10707,7 @@
       <c r="AE209" s="7"/>
       <c r="AF209" s="7"/>
     </row>
-    <row r="210" spans="1:32">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A210" s="7"/>
       <c r="B210" s="7"/>
       <c r="C210" s="7"/>
@@ -10750,7 +10741,7 @@
       <c r="AE210" s="7"/>
       <c r="AF210" s="7"/>
     </row>
-    <row r="211" spans="1:32">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A211" s="7"/>
       <c r="B211" s="7"/>
       <c r="C211" s="7"/>
@@ -10784,7 +10775,7 @@
       <c r="AE211" s="7"/>
       <c r="AF211" s="7"/>
     </row>
-    <row r="212" spans="1:32">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A212" s="7"/>
       <c r="B212" s="7"/>
       <c r="C212" s="7"/>
@@ -10818,7 +10809,7 @@
       <c r="AE212" s="7"/>
       <c r="AF212" s="7"/>
     </row>
-    <row r="213" spans="1:32">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A213" s="7"/>
       <c r="B213" s="7"/>
       <c r="C213" s="7"/>
@@ -10852,7 +10843,7 @@
       <c r="AE213" s="7"/>
       <c r="AF213" s="7"/>
     </row>
-    <row r="214" spans="1:32">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A214" s="7"/>
       <c r="B214" s="7"/>
       <c r="C214" s="7"/>
@@ -10886,7 +10877,7 @@
       <c r="AE214" s="7"/>
       <c r="AF214" s="7"/>
     </row>
-    <row r="215" spans="1:32">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A215" s="7"/>
       <c r="B215" s="7"/>
       <c r="C215" s="7"/>
@@ -10920,7 +10911,7 @@
       <c r="AE215" s="7"/>
       <c r="AF215" s="7"/>
     </row>
-    <row r="216" spans="1:32">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A216" s="7"/>
       <c r="B216" s="7"/>
       <c r="C216" s="7"/>
@@ -10954,7 +10945,7 @@
       <c r="AE216" s="7"/>
       <c r="AF216" s="7"/>
     </row>
-    <row r="217" spans="1:32">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A217" s="7"/>
       <c r="B217" s="7"/>
       <c r="C217" s="7"/>
@@ -10988,7 +10979,7 @@
       <c r="AE217" s="7"/>
       <c r="AF217" s="7"/>
     </row>
-    <row r="218" spans="1:32">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A218" s="7"/>
       <c r="B218" s="7"/>
       <c r="C218" s="7"/>
@@ -11022,7 +11013,7 @@
       <c r="AE218" s="7"/>
       <c r="AF218" s="7"/>
     </row>
-    <row r="219" spans="1:32">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A219" s="7"/>
       <c r="B219" s="7"/>
       <c r="C219" s="7"/>
@@ -11056,7 +11047,7 @@
       <c r="AE219" s="7"/>
       <c r="AF219" s="7"/>
     </row>
-    <row r="220" spans="1:32">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A220" s="7"/>
       <c r="B220" s="7"/>
       <c r="C220" s="7"/>
@@ -11090,7 +11081,7 @@
       <c r="AE220" s="7"/>
       <c r="AF220" s="7"/>
     </row>
-    <row r="221" spans="1:32">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A221" s="7"/>
       <c r="B221" s="7"/>
       <c r="C221" s="7"/>
@@ -11124,7 +11115,7 @@
       <c r="AE221" s="7"/>
       <c r="AF221" s="7"/>
     </row>
-    <row r="222" spans="1:32">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A222" s="7"/>
       <c r="B222" s="7"/>
       <c r="C222" s="7"/>
@@ -11158,7 +11149,7 @@
       <c r="AE222" s="7"/>
       <c r="AF222" s="7"/>
     </row>
-    <row r="223" spans="1:32">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A223" s="7"/>
       <c r="B223" s="7"/>
       <c r="C223" s="7"/>
@@ -11192,7 +11183,7 @@
       <c r="AE223" s="7"/>
       <c r="AF223" s="7"/>
     </row>
-    <row r="224" spans="1:32">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A224" s="7"/>
       <c r="B224" s="7"/>
       <c r="C224" s="7"/>
@@ -11226,7 +11217,7 @@
       <c r="AE224" s="7"/>
       <c r="AF224" s="7"/>
     </row>
-    <row r="225" spans="1:32">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A225" s="7"/>
       <c r="B225" s="7"/>
       <c r="C225" s="7"/>
@@ -11260,7 +11251,7 @@
       <c r="AE225" s="7"/>
       <c r="AF225" s="7"/>
     </row>
-    <row r="226" spans="1:32">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A226" s="7"/>
       <c r="B226" s="7"/>
       <c r="C226" s="7"/>
@@ -11294,7 +11285,7 @@
       <c r="AE226" s="7"/>
       <c r="AF226" s="7"/>
     </row>
-    <row r="227" spans="1:32">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A227" s="7"/>
       <c r="B227" s="7"/>
       <c r="C227" s="7"/>
@@ -11328,7 +11319,7 @@
       <c r="AE227" s="7"/>
       <c r="AF227" s="7"/>
     </row>
-    <row r="228" spans="1:32">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A228" s="7"/>
       <c r="B228" s="7"/>
       <c r="C228" s="7"/>
@@ -11362,7 +11353,7 @@
       <c r="AE228" s="7"/>
       <c r="AF228" s="7"/>
     </row>
-    <row r="229" spans="1:32">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A229" s="7"/>
       <c r="B229" s="7"/>
       <c r="C229" s="7"/>
@@ -11396,7 +11387,7 @@
       <c r="AE229" s="7"/>
       <c r="AF229" s="7"/>
     </row>
-    <row r="230" spans="1:32">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -11430,7 +11421,7 @@
       <c r="AE230" s="7"/>
       <c r="AF230" s="7"/>
     </row>
-    <row r="231" spans="1:32">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -11464,7 +11455,7 @@
       <c r="AE231" s="7"/>
       <c r="AF231" s="7"/>
     </row>
-    <row r="232" spans="1:32">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -11498,7 +11489,7 @@
       <c r="AE232" s="7"/>
       <c r="AF232" s="7"/>
     </row>
-    <row r="233" spans="1:32">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -11532,7 +11523,7 @@
       <c r="AE233" s="7"/>
       <c r="AF233" s="7"/>
     </row>
-    <row r="234" spans="1:32">
+    <row r="234" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A234" s="7"/>
       <c r="B234" s="7"/>
       <c r="C234" s="7"/>
@@ -11566,7 +11557,7 @@
       <c r="AE234" s="7"/>
       <c r="AF234" s="7"/>
     </row>
-    <row r="235" spans="1:32">
+    <row r="235" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A235" s="7"/>
       <c r="B235" s="7"/>
       <c r="C235" s="7"/>
@@ -11600,7 +11591,7 @@
       <c r="AE235" s="7"/>
       <c r="AF235" s="7"/>
     </row>
-    <row r="236" spans="1:32">
+    <row r="236" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A236" s="7"/>
       <c r="B236" s="7"/>
       <c r="C236" s="7"/>
@@ -11634,7 +11625,7 @@
       <c r="AE236" s="7"/>
       <c r="AF236" s="7"/>
     </row>
-    <row r="237" spans="1:32">
+    <row r="237" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A237" s="7"/>
       <c r="B237" s="7"/>
       <c r="C237" s="7"/>
@@ -11668,7 +11659,7 @@
       <c r="AE237" s="7"/>
       <c r="AF237" s="7"/>
     </row>
-    <row r="238" spans="1:32">
+    <row r="238" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A238" s="7"/>
       <c r="B238" s="7"/>
       <c r="C238" s="7"/>
@@ -11702,7 +11693,7 @@
       <c r="AE238" s="7"/>
       <c r="AF238" s="7"/>
     </row>
-    <row r="239" spans="1:32">
+    <row r="239" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A239" s="7"/>
       <c r="B239" s="7"/>
       <c r="C239" s="7"/>
@@ -11736,7 +11727,7 @@
       <c r="AE239" s="7"/>
       <c r="AF239" s="7"/>
     </row>
-    <row r="240" spans="1:32">
+    <row r="240" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A240" s="7"/>
       <c r="B240" s="7"/>
       <c r="C240" s="7"/>
@@ -11770,7 +11761,7 @@
       <c r="AE240" s="7"/>
       <c r="AF240" s="7"/>
     </row>
-    <row r="241" spans="1:32">
+    <row r="241" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A241" s="7"/>
       <c r="B241" s="7"/>
       <c r="C241" s="7"/>
@@ -11804,7 +11795,7 @@
       <c r="AE241" s="7"/>
       <c r="AF241" s="7"/>
     </row>
-    <row r="242" spans="1:32">
+    <row r="242" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A242" s="7"/>
       <c r="B242" s="7"/>
       <c r="C242" s="7"/>
@@ -11838,7 +11829,7 @@
       <c r="AE242" s="7"/>
       <c r="AF242" s="7"/>
     </row>
-    <row r="243" spans="1:32">
+    <row r="243" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A243" s="7"/>
       <c r="B243" s="7"/>
       <c r="C243" s="7"/>
@@ -11872,7 +11863,7 @@
       <c r="AE243" s="7"/>
       <c r="AF243" s="7"/>
     </row>
-    <row r="244" spans="1:32">
+    <row r="244" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A244" s="7"/>
       <c r="B244" s="7"/>
       <c r="C244" s="7"/>
@@ -11906,7 +11897,7 @@
       <c r="AE244" s="7"/>
       <c r="AF244" s="7"/>
     </row>
-    <row r="245" spans="1:32">
+    <row r="245" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A245" s="7"/>
       <c r="B245" s="7"/>
       <c r="C245" s="7"/>
@@ -11940,7 +11931,7 @@
       <c r="AE245" s="7"/>
       <c r="AF245" s="7"/>
     </row>
-    <row r="246" spans="1:32">
+    <row r="246" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A246" s="7"/>
       <c r="B246" s="7"/>
       <c r="C246" s="7"/>
@@ -11974,7 +11965,7 @@
       <c r="AE246" s="7"/>
       <c r="AF246" s="7"/>
     </row>
-    <row r="247" spans="1:32">
+    <row r="247" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A247" s="7"/>
       <c r="B247" s="7"/>
       <c r="C247" s="7"/>
@@ -12008,7 +11999,7 @@
       <c r="AE247" s="7"/>
       <c r="AF247" s="7"/>
     </row>
-    <row r="248" spans="1:32">
+    <row r="248" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A248" s="7"/>
       <c r="B248" s="7"/>
       <c r="C248" s="7"/>
@@ -12042,7 +12033,7 @@
       <c r="AE248" s="7"/>
       <c r="AF248" s="7"/>
     </row>
-    <row r="249" spans="1:32">
+    <row r="249" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A249" s="7"/>
       <c r="B249" s="7"/>
       <c r="C249" s="7"/>
@@ -12076,7 +12067,7 @@
       <c r="AE249" s="7"/>
       <c r="AF249" s="7"/>
     </row>
-    <row r="250" spans="1:32">
+    <row r="250" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A250" s="7"/>
       <c r="B250" s="7"/>
       <c r="C250" s="7"/>
@@ -12110,7 +12101,7 @@
       <c r="AE250" s="7"/>
       <c r="AF250" s="7"/>
     </row>
-    <row r="251" spans="1:32">
+    <row r="251" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A251" s="7"/>
       <c r="B251" s="7"/>
       <c r="C251" s="7"/>
@@ -12144,7 +12135,7 @@
       <c r="AE251" s="7"/>
       <c r="AF251" s="7"/>
     </row>
-    <row r="252" spans="1:32">
+    <row r="252" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A252" s="7"/>
       <c r="B252" s="7"/>
       <c r="C252" s="7"/>
@@ -12178,7 +12169,7 @@
       <c r="AE252" s="7"/>
       <c r="AF252" s="7"/>
     </row>
-    <row r="253" spans="1:32">
+    <row r="253" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A253" s="7"/>
       <c r="B253" s="7"/>
       <c r="C253" s="7"/>
@@ -12212,7 +12203,7 @@
       <c r="AE253" s="7"/>
       <c r="AF253" s="7"/>
     </row>
-    <row r="254" spans="1:32">
+    <row r="254" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A254" s="7"/>
       <c r="B254" s="7"/>
       <c r="C254" s="7"/>
@@ -12246,7 +12237,7 @@
       <c r="AE254" s="7"/>
       <c r="AF254" s="7"/>
     </row>
-    <row r="255" spans="1:32">
+    <row r="255" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A255" s="7"/>
       <c r="B255" s="7"/>
       <c r="C255" s="7"/>
@@ -12280,7 +12271,7 @@
       <c r="AE255" s="7"/>
       <c r="AF255" s="7"/>
     </row>
-    <row r="256" spans="1:32">
+    <row r="256" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A256" s="7"/>
       <c r="B256" s="7"/>
       <c r="C256" s="7"/>
@@ -12314,7 +12305,7 @@
       <c r="AE256" s="7"/>
       <c r="AF256" s="7"/>
     </row>
-    <row r="257" spans="1:32">
+    <row r="257" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A257" s="7"/>
       <c r="B257" s="7"/>
       <c r="C257" s="7"/>
@@ -12348,7 +12339,7 @@
       <c r="AE257" s="7"/>
       <c r="AF257" s="7"/>
     </row>
-    <row r="258" spans="1:32">
+    <row r="258" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A258" s="7"/>
       <c r="B258" s="7"/>
       <c r="C258" s="7"/>
@@ -12382,7 +12373,7 @@
       <c r="AE258" s="7"/>
       <c r="AF258" s="7"/>
     </row>
-    <row r="259" spans="1:32">
+    <row r="259" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A259" s="7"/>
       <c r="B259" s="7"/>
       <c r="C259" s="7"/>
@@ -12416,7 +12407,7 @@
       <c r="AE259" s="7"/>
       <c r="AF259" s="7"/>
     </row>
-    <row r="260" spans="1:32">
+    <row r="260" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A260" s="7"/>
       <c r="B260" s="7"/>
       <c r="C260" s="7"/>
@@ -12450,7 +12441,7 @@
       <c r="AE260" s="7"/>
       <c r="AF260" s="7"/>
     </row>
-    <row r="261" spans="1:32">
+    <row r="261" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A261" s="7"/>
       <c r="B261" s="7"/>
       <c r="C261" s="7"/>
@@ -12484,7 +12475,7 @@
       <c r="AE261" s="7"/>
       <c r="AF261" s="7"/>
     </row>
-    <row r="262" spans="1:32">
+    <row r="262" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A262" s="7"/>
       <c r="B262" s="7"/>
       <c r="C262" s="7"/>
@@ -12518,7 +12509,7 @@
       <c r="AE262" s="7"/>
       <c r="AF262" s="7"/>
     </row>
-    <row r="263" spans="1:32">
+    <row r="263" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A263" s="7"/>
       <c r="B263" s="7"/>
       <c r="C263" s="7"/>
@@ -12552,7 +12543,7 @@
       <c r="AE263" s="7"/>
       <c r="AF263" s="7"/>
     </row>
-    <row r="264" spans="1:32">
+    <row r="264" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A264" s="7"/>
       <c r="B264" s="7"/>
       <c r="C264" s="7"/>
@@ -12586,7 +12577,7 @@
       <c r="AE264" s="7"/>
       <c r="AF264" s="7"/>
     </row>
-    <row r="265" spans="1:32">
+    <row r="265" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A265" s="7"/>
       <c r="B265" s="7"/>
       <c r="C265" s="7"/>
@@ -12620,7 +12611,7 @@
       <c r="AE265" s="7"/>
       <c r="AF265" s="7"/>
     </row>
-    <row r="266" spans="1:32">
+    <row r="266" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A266" s="7"/>
       <c r="B266" s="7"/>
       <c r="C266" s="7"/>
@@ -12654,7 +12645,7 @@
       <c r="AE266" s="7"/>
       <c r="AF266" s="7"/>
     </row>
-    <row r="267" spans="1:32">
+    <row r="267" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A267" s="7"/>
       <c r="B267" s="7"/>
       <c r="C267" s="7"/>
@@ -12688,7 +12679,7 @@
       <c r="AE267" s="7"/>
       <c r="AF267" s="7"/>
     </row>
-    <row r="268" spans="1:32">
+    <row r="268" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A268" s="7"/>
       <c r="B268" s="7"/>
       <c r="C268" s="7"/>
@@ -12722,7 +12713,7 @@
       <c r="AE268" s="7"/>
       <c r="AF268" s="7"/>
     </row>
-    <row r="269" spans="1:32">
+    <row r="269" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A269" s="7"/>
       <c r="B269" s="7"/>
       <c r="C269" s="7"/>
@@ -12756,7 +12747,7 @@
       <c r="AE269" s="7"/>
       <c r="AF269" s="7"/>
     </row>
-    <row r="270" spans="1:32">
+    <row r="270" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A270" s="7"/>
       <c r="B270" s="7"/>
       <c r="C270" s="7"/>
@@ -12790,7 +12781,7 @@
       <c r="AE270" s="7"/>
       <c r="AF270" s="7"/>
     </row>
-    <row r="271" spans="1:32">
+    <row r="271" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A271" s="7"/>
       <c r="B271" s="7"/>
       <c r="C271" s="7"/>
@@ -12824,7 +12815,7 @@
       <c r="AE271" s="7"/>
       <c r="AF271" s="7"/>
     </row>
-    <row r="272" spans="1:32">
+    <row r="272" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A272" s="7"/>
       <c r="B272" s="7"/>
       <c r="C272" s="7"/>
@@ -12858,7 +12849,7 @@
       <c r="AE272" s="7"/>
       <c r="AF272" s="7"/>
     </row>
-    <row r="273" spans="1:32">
+    <row r="273" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A273" s="7"/>
       <c r="B273" s="7"/>
       <c r="C273" s="7"/>
@@ -12892,7 +12883,7 @@
       <c r="AE273" s="7"/>
       <c r="AF273" s="7"/>
     </row>
-    <row r="274" spans="1:32">
+    <row r="274" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A274" s="7"/>
       <c r="B274" s="7"/>
       <c r="C274" s="7"/>
@@ -12926,7 +12917,7 @@
       <c r="AE274" s="7"/>
       <c r="AF274" s="7"/>
     </row>
-    <row r="275" spans="1:32">
+    <row r="275" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A275" s="7"/>
       <c r="B275" s="7"/>
       <c r="C275" s="7"/>
@@ -12960,7 +12951,7 @@
       <c r="AE275" s="7"/>
       <c r="AF275" s="7"/>
     </row>
-    <row r="276" spans="1:32">
+    <row r="276" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A276" s="7"/>
       <c r="B276" s="7"/>
       <c r="C276" s="7"/>
@@ -12994,7 +12985,7 @@
       <c r="AE276" s="7"/>
       <c r="AF276" s="7"/>
     </row>
-    <row r="277" spans="1:32">
+    <row r="277" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A277" s="7"/>
       <c r="B277" s="7"/>
       <c r="C277" s="7"/>
@@ -13028,7 +13019,7 @@
       <c r="AE277" s="7"/>
       <c r="AF277" s="7"/>
     </row>
-    <row r="278" spans="1:32">
+    <row r="278" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A278" s="7"/>
       <c r="B278" s="7"/>
       <c r="C278" s="7"/>
@@ -13062,7 +13053,7 @@
       <c r="AE278" s="7"/>
       <c r="AF278" s="7"/>
     </row>
-    <row r="279" spans="1:32">
+    <row r="279" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A279" s="7"/>
       <c r="B279" s="7"/>
       <c r="C279" s="7"/>
@@ -13096,7 +13087,7 @@
       <c r="AE279" s="7"/>
       <c r="AF279" s="7"/>
     </row>
-    <row r="280" spans="1:32">
+    <row r="280" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A280" s="7"/>
       <c r="B280" s="7"/>
       <c r="C280" s="7"/>
@@ -13130,7 +13121,7 @@
       <c r="AE280" s="7"/>
       <c r="AF280" s="7"/>
     </row>
-    <row r="281" spans="1:32">
+    <row r="281" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A281" s="7"/>
       <c r="B281" s="7"/>
       <c r="C281" s="7"/>
@@ -13164,7 +13155,7 @@
       <c r="AE281" s="7"/>
       <c r="AF281" s="7"/>
     </row>
-    <row r="282" spans="1:32">
+    <row r="282" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A282" s="7"/>
       <c r="B282" s="7"/>
       <c r="C282" s="7"/>
@@ -13198,7 +13189,7 @@
       <c r="AE282" s="7"/>
       <c r="AF282" s="7"/>
     </row>
-    <row r="283" spans="1:32">
+    <row r="283" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A283" s="7"/>
       <c r="B283" s="7"/>
       <c r="C283" s="7"/>
@@ -13232,7 +13223,7 @@
       <c r="AE283" s="7"/>
       <c r="AF283" s="7"/>
     </row>
-    <row r="284" spans="1:32">
+    <row r="284" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A284" s="7"/>
       <c r="B284" s="7"/>
       <c r="C284" s="7"/>
@@ -13266,7 +13257,7 @@
       <c r="AE284" s="7"/>
       <c r="AF284" s="7"/>
     </row>
-    <row r="285" spans="1:32">
+    <row r="285" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A285" s="7"/>
       <c r="B285" s="7"/>
       <c r="C285" s="7"/>
@@ -13300,7 +13291,7 @@
       <c r="AE285" s="7"/>
       <c r="AF285" s="7"/>
     </row>
-    <row r="286" spans="1:32">
+    <row r="286" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A286" s="7"/>
       <c r="B286" s="7"/>
       <c r="C286" s="7"/>
@@ -13334,7 +13325,7 @@
       <c r="AE286" s="7"/>
       <c r="AF286" s="7"/>
     </row>
-    <row r="287" spans="1:32">
+    <row r="287" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A287" s="7"/>
       <c r="B287" s="7"/>
       <c r="C287" s="7"/>
@@ -13368,7 +13359,7 @@
       <c r="AE287" s="7"/>
       <c r="AF287" s="7"/>
     </row>
-    <row r="288" spans="1:32">
+    <row r="288" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A288" s="7"/>
       <c r="B288" s="7"/>
       <c r="C288" s="7"/>
@@ -13402,7 +13393,7 @@
       <c r="AE288" s="7"/>
       <c r="AF288" s="7"/>
     </row>
-    <row r="289" spans="1:32">
+    <row r="289" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A289" s="7"/>
       <c r="B289" s="7"/>
       <c r="C289" s="7"/>
@@ -13436,7 +13427,7 @@
       <c r="AE289" s="7"/>
       <c r="AF289" s="7"/>
     </row>
-    <row r="290" spans="1:32">
+    <row r="290" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A290" s="7"/>
       <c r="B290" s="7"/>
       <c r="C290" s="7"/>
@@ -13470,7 +13461,7 @@
       <c r="AE290" s="7"/>
       <c r="AF290" s="7"/>
     </row>
-    <row r="291" spans="1:32">
+    <row r="291" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A291" s="7"/>
       <c r="B291" s="7"/>
       <c r="C291" s="7"/>
@@ -13504,7 +13495,7 @@
       <c r="AE291" s="7"/>
       <c r="AF291" s="7"/>
     </row>
-    <row r="292" spans="1:32">
+    <row r="292" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A292" s="7"/>
       <c r="B292" s="7"/>
       <c r="C292" s="7"/>
@@ -13538,7 +13529,7 @@
       <c r="AE292" s="7"/>
       <c r="AF292" s="7"/>
     </row>
-    <row r="293" spans="1:32">
+    <row r="293" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A293" s="7"/>
       <c r="B293" s="7"/>
       <c r="C293" s="7"/>
@@ -13572,7 +13563,7 @@
       <c r="AE293" s="7"/>
       <c r="AF293" s="7"/>
     </row>
-    <row r="294" spans="1:32">
+    <row r="294" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A294" s="7"/>
       <c r="B294" s="7"/>
       <c r="C294" s="7"/>
@@ -13606,7 +13597,7 @@
       <c r="AE294" s="7"/>
       <c r="AF294" s="7"/>
     </row>
-    <row r="295" spans="1:32">
+    <row r="295" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A295" s="7"/>
       <c r="B295" s="7"/>
       <c r="C295" s="7"/>
@@ -13640,7 +13631,7 @@
       <c r="AE295" s="7"/>
       <c r="AF295" s="7"/>
     </row>
-    <row r="296" spans="1:32">
+    <row r="296" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A296" s="7"/>
       <c r="B296" s="7"/>
       <c r="C296" s="7"/>
@@ -13674,7 +13665,7 @@
       <c r="AE296" s="7"/>
       <c r="AF296" s="7"/>
     </row>
-    <row r="297" spans="1:32">
+    <row r="297" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A297" s="7"/>
       <c r="B297" s="7"/>
       <c r="C297" s="7"/>
@@ -14102,7 +14093,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AF233"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
@@ -14123,15 +14114,15 @@
     <col min="19" max="19" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" thickBot="1">
+    <row r="1" spans="1:32" ht="15.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14157,26 +14148,26 @@
       <c r="AE1" s="7"/>
       <c r="AF1" s="7"/>
     </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1">
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="119" t="s">
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="120"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="121"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14193,24 +14184,24 @@
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
     </row>
-    <row r="3" spans="1:32" ht="15" customHeight="1">
+    <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="123"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="123"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="124"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="143"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="160"/>
+      <c r="Q3" s="161"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14227,24 +14218,24 @@
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
     </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="4" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="174"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="126"/>
-      <c r="P4" s="126"/>
-      <c r="Q4" s="127"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="162"/>
+      <c r="J4" s="163"/>
+      <c r="K4" s="163"/>
+      <c r="L4" s="163"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="164"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14261,26 +14252,26 @@
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
     </row>
-    <row r="5" spans="1:32" ht="24.75" customHeight="1">
+    <row r="5" spans="1:32" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="128" t="s">
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="165" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="129"/>
-      <c r="K5" s="129"/>
-      <c r="L5" s="129"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="129"/>
-      <c r="O5" s="129"/>
-      <c r="P5" s="129"/>
-      <c r="Q5" s="130"/>
+      <c r="J5" s="166"/>
+      <c r="K5" s="166"/>
+      <c r="L5" s="166"/>
+      <c r="M5" s="166"/>
+      <c r="N5" s="166"/>
+      <c r="O5" s="166"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="167"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14297,15 +14288,15 @@
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
     </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1">
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="174"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
       <c r="I6" s="50" t="s">
         <v>51</v>
       </c>
@@ -14315,14 +14306,14 @@
       <c r="K6" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="171" t="s">
+      <c r="L6" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="172"/>
-      <c r="N6" s="172"/>
-      <c r="O6" s="172"/>
-      <c r="P6" s="172"/>
-      <c r="Q6" s="173"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="137"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14339,15 +14330,15 @@
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
     </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="7" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="174"/>
-      <c r="H7" s="174"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
       <c r="I7" s="51" t="s">
         <v>21</v>
       </c>
@@ -14359,14 +14350,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="165" t="s">
+      <c r="L7" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="166"/>
-      <c r="N7" s="166"/>
-      <c r="O7" s="166"/>
-      <c r="P7" s="166"/>
-      <c r="Q7" s="167"/>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="120"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14383,17 +14374,17 @@
       <c r="AE7" s="7"/>
       <c r="AF7" s="7"/>
     </row>
-    <row r="8" spans="1:32" ht="15" customHeight="1">
+    <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="146" t="s">
+      <c r="B8" s="181" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="147"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="174"/>
-      <c r="H8" s="174"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="182"/>
+      <c r="E8" s="182"/>
+      <c r="F8" s="183"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14405,14 +14396,14 @@
         <f>J8/J7</f>
         <v>0.99739525237691695</v>
       </c>
-      <c r="L8" s="165" t="s">
+      <c r="L8" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="166"/>
-      <c r="N8" s="166"/>
-      <c r="O8" s="166"/>
-      <c r="P8" s="166"/>
-      <c r="Q8" s="167"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="120"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14429,15 +14420,15 @@
       <c r="AE8" s="7"/>
       <c r="AF8" s="7"/>
     </row>
-    <row r="9" spans="1:32" ht="15" customHeight="1">
+    <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="149"/>
-      <c r="C9" s="150"/>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="151"/>
-      <c r="G9" s="174"/>
-      <c r="H9" s="174"/>
+      <c r="B9" s="184"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="185"/>
+      <c r="F9" s="186"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14449,14 +14440,14 @@
         <f>J9/J7</f>
         <v>2.4135299294340269E-3</v>
       </c>
-      <c r="L9" s="165" t="s">
+      <c r="L9" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="166"/>
-      <c r="N9" s="166"/>
-      <c r="O9" s="166"/>
-      <c r="P9" s="166"/>
-      <c r="Q9" s="167"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="120"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14473,15 +14464,15 @@
       <c r="AE9" s="7"/>
       <c r="AF9" s="7"/>
     </row>
-    <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="152"/>
-      <c r="C10" s="153"/>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="174"/>
-      <c r="H10" s="174"/>
+      <c r="B10" s="187"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
+      <c r="F10" s="189"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14493,14 +14484,14 @@
         <f>J10/J7</f>
         <v>1.9121769364906241E-4</v>
       </c>
-      <c r="L10" s="165" t="s">
+      <c r="L10" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="166"/>
-      <c r="N10" s="166"/>
-      <c r="O10" s="166"/>
-      <c r="P10" s="166"/>
-      <c r="Q10" s="167"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="120"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14517,26 +14508,26 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="7"/>
     </row>
-    <row r="11" spans="1:32" ht="15" customHeight="1">
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="146" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="157"/>
-      <c r="G11" s="174"/>
-      <c r="H11" s="174"/>
-      <c r="I11" s="190"/>
-      <c r="J11" s="190"/>
-      <c r="K11" s="190"/>
-      <c r="L11" s="190"/>
-      <c r="M11" s="190"/>
-      <c r="N11" s="190"/>
-      <c r="O11" s="190"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="134"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="134"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
+      <c r="N11" s="134"/>
+      <c r="O11" s="134"/>
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14553,15 +14544,15 @@
       <c r="AE11" s="7"/>
       <c r="AF11" s="7"/>
     </row>
-    <row r="12" spans="1:32" ht="15" customHeight="1">
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="158"/>
-      <c r="C12" s="159"/>
-      <c r="D12" s="159"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="160"/>
-      <c r="G12" s="174"/>
-      <c r="H12" s="174"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="150"/>
+      <c r="E12" s="150"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
       <c r="I12" s="50" t="s">
         <v>53</v>
       </c>
@@ -14571,14 +14562,14 @@
       <c r="K12" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="171" t="s">
+      <c r="L12" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="172"/>
-      <c r="N12" s="172"/>
-      <c r="O12" s="172"/>
-      <c r="P12" s="172"/>
-      <c r="Q12" s="173"/>
+      <c r="M12" s="136"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="136"/>
+      <c r="P12" s="136"/>
+      <c r="Q12" s="137"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14595,19 +14586,19 @@
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
     </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1">
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="144" t="s">
+      <c r="B13" s="138" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="145"/>
-      <c r="D13" s="134" t="s">
+      <c r="C13" s="139"/>
+      <c r="D13" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="134"/>
-      <c r="F13" s="134"/>
-      <c r="G13" s="174"/>
-      <c r="H13" s="174"/>
+      <c r="E13" s="171"/>
+      <c r="F13" s="171"/>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14619,14 +14610,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="165" t="s">
+      <c r="L13" s="118" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="166"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="166"/>
-      <c r="Q13" s="167"/>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="120"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14643,7 +14634,7 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="7"/>
     </row>
-    <row r="14" spans="1:32" ht="15" customHeight="1">
+    <row r="14" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="7"/>
       <c r="B14" s="4" t="s">
         <v>35</v>
@@ -14651,13 +14642,13 @@
       <c r="C14" s="44">
         <v>220</v>
       </c>
-      <c r="D14" s="135" t="s">
+      <c r="D14" s="172" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="174"/>
-      <c r="H14" s="174"/>
+      <c r="E14" s="172"/>
+      <c r="F14" s="172"/>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
       <c r="I14" s="52" t="s">
         <v>45</v>
       </c>
@@ -14669,14 +14660,14 @@
         <f>J14/J13</f>
         <v>0.99741000000000002</v>
       </c>
-      <c r="L14" s="168" t="s">
+      <c r="L14" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="169"/>
-      <c r="N14" s="169"/>
-      <c r="O14" s="169"/>
-      <c r="P14" s="169"/>
-      <c r="Q14" s="170"/>
+      <c r="M14" s="141"/>
+      <c r="N14" s="141"/>
+      <c r="O14" s="141"/>
+      <c r="P14" s="141"/>
+      <c r="Q14" s="142"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14693,7 +14684,7 @@
       <c r="AE14" s="7"/>
       <c r="AF14" s="7"/>
     </row>
-    <row r="15" spans="1:32" ht="15" customHeight="1">
+    <row r="15" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
       <c r="B15" s="5" t="s">
         <v>15</v>
@@ -14701,13 +14692,13 @@
       <c r="C15" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="136" t="s">
+      <c r="D15" s="173" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="174"/>
-      <c r="H15" s="174"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
       <c r="I15" s="51" t="s">
         <v>46</v>
       </c>
@@ -14719,14 +14710,14 @@
         <f>J15/J13</f>
         <v>2.4000000000000007E-3</v>
       </c>
-      <c r="L15" s="165" t="s">
+      <c r="L15" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="166"/>
-      <c r="N15" s="166"/>
-      <c r="O15" s="166"/>
-      <c r="P15" s="166"/>
-      <c r="Q15" s="167"/>
+      <c r="M15" s="119"/>
+      <c r="N15" s="119"/>
+      <c r="O15" s="119"/>
+      <c r="P15" s="119"/>
+      <c r="Q15" s="120"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14743,7 +14734,7 @@
       <c r="AE15" s="7"/>
       <c r="AF15" s="7"/>
     </row>
-    <row r="16" spans="1:32" ht="15" customHeight="1">
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="7"/>
       <c r="B16" s="4" t="s">
         <v>36</v>
@@ -14751,13 +14742,13 @@
       <c r="C16" s="45">
         <v>0.9</v>
       </c>
-      <c r="D16" s="137" t="s">
+      <c r="D16" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="138"/>
-      <c r="F16" s="139"/>
-      <c r="G16" s="174"/>
-      <c r="H16" s="174"/>
+      <c r="E16" s="175"/>
+      <c r="F16" s="176"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
       <c r="I16" s="52" t="s">
         <v>47</v>
       </c>
@@ -14769,14 +14760,14 @@
         <f>J16/J13</f>
         <v>1.9000000000000001E-4</v>
       </c>
-      <c r="L16" s="165" t="s">
+      <c r="L16" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="166"/>
-      <c r="N16" s="166"/>
-      <c r="O16" s="166"/>
-      <c r="P16" s="166"/>
-      <c r="Q16" s="167"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="120"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14793,7 +14784,7 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="7"/>
     </row>
-    <row r="17" spans="1:32" ht="15" customHeight="1">
+    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="7"/>
       <c r="B17" s="5" t="s">
         <v>16</v>
@@ -14801,22 +14792,22 @@
       <c r="C17" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="140" t="s">
+      <c r="D17" s="177" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="141"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="174"/>
-      <c r="H17" s="174"/>
-      <c r="I17" s="168"/>
-      <c r="J17" s="169"/>
-      <c r="K17" s="169"/>
-      <c r="L17" s="169"/>
-      <c r="M17" s="169"/>
-      <c r="N17" s="169"/>
-      <c r="O17" s="169"/>
-      <c r="P17" s="169"/>
-      <c r="Q17" s="170"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="141"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="141"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="141"/>
+      <c r="O17" s="141"/>
+      <c r="P17" s="141"/>
+      <c r="Q17" s="142"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14833,7 +14824,7 @@
       <c r="AE17" s="7"/>
       <c r="AF17" s="7"/>
     </row>
-    <row r="18" spans="1:32" ht="15" customHeight="1">
+    <row r="18" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="7"/>
       <c r="B18" s="4" t="s">
         <v>37</v>
@@ -14841,13 +14832,13 @@
       <c r="C18" s="45">
         <v>0.1</v>
       </c>
-      <c r="D18" s="137" t="s">
+      <c r="D18" s="174" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="138"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="174"/>
-      <c r="H18" s="174"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
       <c r="I18" s="50" t="s">
         <v>31</v>
       </c>
@@ -14857,14 +14848,14 @@
       <c r="K18" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="171" t="s">
+      <c r="L18" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="M18" s="172"/>
-      <c r="N18" s="172"/>
-      <c r="O18" s="172"/>
-      <c r="P18" s="172"/>
-      <c r="Q18" s="173"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="137"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14881,15 +14872,15 @@
       <c r="AE18" s="7"/>
       <c r="AF18" s="7"/>
     </row>
-    <row r="19" spans="1:32" ht="15" customHeight="1">
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="174"/>
+      <c r="B19" s="173"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="143"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14901,14 +14892,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="165" t="s">
+      <c r="L19" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="166"/>
-      <c r="N19" s="166"/>
-      <c r="O19" s="166"/>
-      <c r="P19" s="166"/>
-      <c r="Q19" s="167"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="120"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14925,19 +14916,19 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="7"/>
     </row>
-    <row r="20" spans="1:32" ht="15" customHeight="1">
+    <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="144" t="s">
+      <c r="B20" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="145"/>
-      <c r="D20" s="134" t="s">
+      <c r="C20" s="139"/>
+      <c r="D20" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="134"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="174"/>
+      <c r="E20" s="171"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
       <c r="I20" s="52" t="s">
         <v>45</v>
       </c>
@@ -14949,14 +14940,14 @@
         <f>J20/J19</f>
         <v>0.94399999999999995</v>
       </c>
-      <c r="L20" s="165" t="s">
+      <c r="L20" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M20" s="166"/>
-      <c r="N20" s="166"/>
-      <c r="O20" s="166"/>
-      <c r="P20" s="166"/>
-      <c r="Q20" s="167"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="120"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14973,7 +14964,7 @@
       <c r="AE20" s="7"/>
       <c r="AF20" s="7"/>
     </row>
-    <row r="21" spans="1:32" ht="15" customHeight="1">
+    <row r="21" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="7"/>
       <c r="B21" s="4" t="s">
         <v>10</v>
@@ -14981,13 +14972,13 @@
       <c r="C21" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="140" t="s">
+      <c r="D21" s="177" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="141"/>
-      <c r="F21" s="142"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="174"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
       <c r="I21" s="51" t="s">
         <v>46</v>
       </c>
@@ -14999,14 +14990,14 @@
         <f>J21/J19</f>
         <v>5.1399999999999994E-2</v>
       </c>
-      <c r="L21" s="165" t="s">
+      <c r="L21" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M21" s="166"/>
-      <c r="N21" s="166"/>
-      <c r="O21" s="166"/>
-      <c r="P21" s="166"/>
-      <c r="Q21" s="167"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="120"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -15023,7 +15014,7 @@
       <c r="AE21" s="7"/>
       <c r="AF21" s="7"/>
     </row>
-    <row r="22" spans="1:32" ht="15" customHeight="1" thickBot="1">
+    <row r="22" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="7"/>
       <c r="B22" s="6" t="s">
         <v>19</v>
@@ -15031,13 +15022,13 @@
       <c r="C22" s="46">
         <v>20000</v>
       </c>
-      <c r="D22" s="143" t="s">
+      <c r="D22" s="180" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="143"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="174"/>
-      <c r="H22" s="174"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="180"/>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
       <c r="I22" s="53" t="s">
         <v>47</v>
       </c>
@@ -15049,14 +15040,14 @@
         <f>J22/J19</f>
         <v>4.5999999999999991E-3</v>
       </c>
-      <c r="L22" s="165" t="s">
+      <c r="L22" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="166"/>
-      <c r="N22" s="166"/>
-      <c r="O22" s="166"/>
-      <c r="P22" s="166"/>
-      <c r="Q22" s="167"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="120"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -15073,24 +15064,24 @@
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
     </row>
-    <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1">
+    <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="174"/>
-      <c r="H23" s="174"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="186"/>
-      <c r="K23" s="186"/>
-      <c r="L23" s="186"/>
-      <c r="M23" s="186"/>
-      <c r="N23" s="186"/>
-      <c r="O23" s="186"/>
-      <c r="P23" s="186"/>
-      <c r="Q23" s="187"/>
+      <c r="B23" s="168"/>
+      <c r="C23" s="169"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="130"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="130"/>
+      <c r="N23" s="130"/>
+      <c r="O23" s="130"/>
+      <c r="P23" s="130"/>
+      <c r="Q23" s="131"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -15107,28 +15098,28 @@
       <c r="AE23" s="7"/>
       <c r="AF23" s="7"/>
     </row>
-    <row r="24" spans="1:32" ht="15" customHeight="1">
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="155" t="s">
+      <c r="B24" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="156"/>
-      <c r="D24" s="156"/>
-      <c r="E24" s="156"/>
-      <c r="F24" s="157"/>
-      <c r="G24" s="174"/>
-      <c r="H24" s="174"/>
-      <c r="I24" s="179" t="s">
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147"/>
+      <c r="F24" s="148"/>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="123" t="s">
         <v>44</v>
       </c>
-      <c r="J24" s="180"/>
-      <c r="K24" s="180"/>
-      <c r="L24" s="180"/>
-      <c r="M24" s="180"/>
-      <c r="N24" s="180"/>
-      <c r="O24" s="180"/>
-      <c r="P24" s="180"/>
-      <c r="Q24" s="181"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="124"/>
+      <c r="L24" s="124"/>
+      <c r="M24" s="124"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="124"/>
+      <c r="P24" s="124"/>
+      <c r="Q24" s="125"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15145,24 +15136,24 @@
       <c r="AE24" s="7"/>
       <c r="AF24" s="7"/>
     </row>
-    <row r="25" spans="1:32" ht="15" customHeight="1">
+    <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="158"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="160"/>
-      <c r="G25" s="174"/>
-      <c r="H25" s="174"/>
-      <c r="I25" s="182"/>
-      <c r="J25" s="183"/>
-      <c r="K25" s="183"/>
-      <c r="L25" s="183"/>
-      <c r="M25" s="183"/>
-      <c r="N25" s="183"/>
-      <c r="O25" s="183"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="184"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="150"/>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="127"/>
+      <c r="P25" s="127"/>
+      <c r="Q25" s="128"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15179,50 +15170,50 @@
       <c r="AE25" s="7"/>
       <c r="AF25" s="7"/>
     </row>
-    <row r="26" spans="1:32" ht="19.5" customHeight="1">
+    <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="177" t="s">
+      <c r="B26" s="144" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="177" t="s">
+      <c r="C26" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="161" t="s">
+      <c r="D26" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="161" t="s">
+      <c r="E26" s="152" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="163" t="s">
+      <c r="F26" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="174"/>
-      <c r="H26" s="174"/>
-      <c r="I26" s="188" t="s">
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="132" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="188" t="s">
+      <c r="J26" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="175" t="s">
+      <c r="K26" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="L26" s="175" t="s">
+      <c r="L26" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="175" t="s">
+      <c r="M26" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="175" t="s">
+      <c r="N26" s="121" t="s">
         <v>64</v>
       </c>
-      <c r="O26" s="175" t="s">
+      <c r="O26" s="121" t="s">
         <v>75</v>
       </c>
-      <c r="P26" s="175" t="s">
+      <c r="P26" s="121" t="s">
         <v>66</v>
       </c>
-      <c r="Q26" s="175" t="s">
+      <c r="Q26" s="121" t="s">
         <v>67</v>
       </c>
       <c r="R26" s="9"/>
@@ -15241,24 +15232,24 @@
       <c r="AE26" s="7"/>
       <c r="AF26" s="7"/>
     </row>
-    <row r="27" spans="1:32" ht="19.5" customHeight="1">
+    <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="178"/>
-      <c r="C27" s="178"/>
-      <c r="D27" s="162"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="174"/>
-      <c r="H27" s="174"/>
-      <c r="I27" s="189"/>
-      <c r="J27" s="189"/>
-      <c r="K27" s="176"/>
-      <c r="L27" s="176"/>
-      <c r="M27" s="176"/>
-      <c r="N27" s="176"/>
-      <c r="O27" s="176"/>
-      <c r="P27" s="176"/>
-      <c r="Q27" s="176"/>
+      <c r="B27" s="145"/>
+      <c r="C27" s="145"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="155"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="143"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="133"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="122"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -15275,15 +15266,15 @@
       <c r="AE27" s="7"/>
       <c r="AF27" s="7"/>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A28" s="94" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B28" s="95" t="s">
         <v>80</v>
       </c>
       <c r="C28" s="93" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D28" s="48">
         <v>6.5247999999999973E-2</v>
@@ -15294,8 +15285,8 @@
       <c r="F28" s="58">
         <v>3.6800000000000001E-3</v>
       </c>
-      <c r="G28" s="174"/>
-      <c r="H28" s="174"/>
+      <c r="G28" s="143"/>
+      <c r="H28" s="143"/>
       <c r="I28" s="55">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
         <v>1.8612811933016251E-4</v>
@@ -15351,66 +15342,66 @@
       <c r="AE28" s="7"/>
       <c r="AF28" s="7"/>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" s="94" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B29" s="95" t="s">
         <v>81</v>
       </c>
       <c r="C29" s="93" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D29" s="48">
-        <v>2.1823520000000003</v>
+        <v>2.31</v>
       </c>
       <c r="E29" s="48">
-        <v>2.5882690000000008</v>
+        <v>2.58</v>
       </c>
       <c r="F29" s="58">
         <v>8.6300000000000005E-4</v>
       </c>
-      <c r="G29" s="174"/>
-      <c r="H29" s="174"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="143"/>
       <c r="I29" s="55">
         <f t="shared" si="1"/>
-        <v>0.15723362449797995</v>
+        <v>0.19303079509931281</v>
       </c>
       <c r="J29" s="55">
         <f t="shared" si="2"/>
-        <v>1.0231882531561007</v>
+        <v>1.120159319649946</v>
       </c>
       <c r="K29" s="56">
         <f t="shared" si="3"/>
-        <v>0.693042745094543</v>
+        <v>0.63801352511300069</v>
       </c>
       <c r="L29" s="56">
         <f t="shared" si="4"/>
-        <v>2.0243888774789092E-3</v>
+        <v>2.3298870781926868E-3</v>
       </c>
       <c r="M29" s="56">
         <f t="shared" si="5"/>
-        <v>0.99797561112252109</v>
+        <v>0.99767011292180729</v>
       </c>
       <c r="N29" s="56">
         <f t="shared" si="6"/>
-        <v>3.4208381037675493E-4</v>
+        <v>3.0898214570041638E-4</v>
       </c>
       <c r="O29" s="57">
         <f t="shared" si="7"/>
-        <v>5.998146012873006E-4</v>
+        <v>5.5218791465648205E-4</v>
       </c>
       <c r="P29" s="57">
         <f t="shared" si="8"/>
-        <v>6.3271085691445897E-3</v>
+        <v>7.2819252573302967E-3</v>
       </c>
       <c r="Q29" s="57">
         <f t="shared" si="9"/>
-        <v>0.23242670934027609</v>
+        <v>0.20993598992875778</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" ref="R29:R39" si="10">O29/F29</f>
-        <v>0.695034300448784</v>
+        <f t="shared" ref="R29:R35" si="10">O29/F29</f>
+        <v>0.63984694629951566</v>
       </c>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
@@ -15427,64 +15418,67 @@
       <c r="AE29" s="7"/>
       <c r="AF29" s="7"/>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" s="96" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="97" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="93" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="98">
-        <v>0.35</v>
-      </c>
-      <c r="E30" s="98">
-        <v>0.53</v>
-      </c>
-      <c r="F30" s="99">
-        <v>4.5100000000000001E-4</v>
-      </c>
-      <c r="G30" s="174"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="104">
-        <f t="shared" si="1"/>
-        <v>1.4856678969095052E-3</v>
-      </c>
-      <c r="J30" s="104">
-        <f t="shared" si="2"/>
-        <v>3.1269911385632183E-2</v>
-      </c>
-      <c r="K30" s="105">
-        <f t="shared" si="3"/>
-        <v>0.99370986963868468</v>
-      </c>
-      <c r="L30" s="105">
-        <f t="shared" si="4"/>
-        <v>2.9571624469205309E-4</v>
-      </c>
-      <c r="M30" s="105">
-        <f t="shared" si="5"/>
-        <v>0.99970428375530795</v>
-      </c>
-      <c r="N30" s="105">
-        <f t="shared" si="6"/>
-        <v>4.2890696890696657E-6</v>
-      </c>
-      <c r="O30" s="106">
-        <f t="shared" si="7"/>
-        <v>4.4945101076502848E-4</v>
-      </c>
-      <c r="P30" s="106">
-        <f t="shared" si="8"/>
-        <v>4.8300571878924151E-4</v>
-      </c>
-      <c r="Q30" s="106">
-        <f t="shared" si="9"/>
-        <v>1.522938484685878E-3</v>
-      </c>
-      <c r="R30" s="9"/>
+        <v>87</v>
+      </c>
+      <c r="B30" s="99" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="190" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="191">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E30" s="191">
+        <v>2.64</v>
+      </c>
+      <c r="F30" s="192">
+        <v>8.9400000000000005E-5</v>
+      </c>
+      <c r="G30" s="143"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="103">
+        <f>IF(D30=0,"",LOG($K$15*10^D30+$K$16*10^E30+$K$14))</f>
+        <v>1.7879251431500753</v>
+      </c>
+      <c r="J30" s="103">
+        <f>IF(D30=0,"",LOG($K$21*10^D30+$K$22*10^E30+$K$20))</f>
+        <v>3.1119549496757086</v>
+      </c>
+      <c r="K30" s="104">
+        <f>IF(D30=0,"",1/(1+10^D30*$J$15/$J$14+10^E30*$J$16/$J$14+10^J30*$J$19/$J$14))</f>
+        <v>1.615944421786869E-2</v>
+      </c>
+      <c r="L30" s="104">
+        <f>IF(D30=0,"",1/(1+10^I30/10^J30*$J$13/$J$19))</f>
+        <v>5.7906462822695359E-3</v>
+      </c>
+      <c r="M30" s="104">
+        <f>IF(D30=0,"",1-L30)</f>
+        <v>0.99420935371773045</v>
+      </c>
+      <c r="N30" s="104">
+        <f>IF(D30=0,"",1/(1/10^E30*$J$20/$J$22+10^D30/10^E30*$J$21/$J$22+10^I30/10^E30*$J$13/$J$22+1))</f>
+        <v>8.9852449106617746E-6</v>
+      </c>
+      <c r="O30" s="105">
+        <f>IF(D30=0,"",F30*K30*$J$7/$J$14)</f>
+        <v>1.4488057294981671E-6</v>
+      </c>
+      <c r="P30" s="105">
+        <f>IF(D30=0,"",O30*10^J30)</f>
+        <v>1.8748438584103456E-3</v>
+      </c>
+      <c r="Q30" s="105">
+        <f>IF(D30=0,"",F30*N30*$J$7/$J$22)</f>
+        <v>6.3242663876621338E-4</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="10"/>
+        <v>1.6205880643156232E-2</v>
+      </c>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
@@ -15500,64 +15494,67 @@
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A31" s="96" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="95" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="190" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="97" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="93" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" s="98">
-        <v>0.35</v>
-      </c>
-      <c r="E31" s="98">
-        <v>0.53</v>
-      </c>
-      <c r="F31" s="99">
-        <v>7.8899999999999999E-4</v>
-      </c>
-      <c r="G31" s="174"/>
-      <c r="H31" s="174"/>
-      <c r="I31" s="104">
-        <f t="shared" si="1"/>
-        <v>1.4856678969095052E-3</v>
-      </c>
-      <c r="J31" s="104">
-        <f t="shared" si="2"/>
-        <v>3.1269911385632183E-2</v>
-      </c>
-      <c r="K31" s="105">
-        <f t="shared" si="3"/>
-        <v>0.99370986963868468</v>
-      </c>
-      <c r="L31" s="105">
-        <f t="shared" si="4"/>
-        <v>2.9571624469205309E-4</v>
-      </c>
-      <c r="M31" s="105">
-        <f t="shared" si="5"/>
-        <v>0.99970428375530795</v>
-      </c>
-      <c r="N31" s="105">
-        <f t="shared" si="6"/>
-        <v>4.2890696890696657E-6</v>
-      </c>
-      <c r="O31" s="106">
-        <f t="shared" si="7"/>
-        <v>7.8629012748028255E-4</v>
-      </c>
-      <c r="P31" s="106">
-        <f t="shared" si="8"/>
-        <v>8.4499226635191018E-4</v>
-      </c>
-      <c r="Q31" s="106">
-        <f t="shared" si="9"/>
-        <v>2.664298147266425E-3</v>
-      </c>
-      <c r="R31" s="9"/>
+      <c r="D31" s="191">
+        <v>-0.92190615231165807</v>
+      </c>
+      <c r="E31" s="191">
+        <v>-1.7889087518799642</v>
+      </c>
+      <c r="F31" s="192">
+        <v>3.1599999999999998E-4</v>
+      </c>
+      <c r="G31" s="143"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="103">
+        <f>IF(D31=0,"",LOG($K$15*10^D31+$K$16*10^E31+$K$14))</f>
+        <v>-9.9986716136098554E-4</v>
+      </c>
+      <c r="J31" s="103">
+        <f>IF(D31=0,"",LOG($K$21*10^D31+$K$22*10^E31+$K$20))</f>
+        <v>-2.2172466001474163E-2</v>
+      </c>
+      <c r="K31" s="104">
+        <f>IF(D31=0,"",1/(1+10^D31*$J$15/$J$14+10^E31*$J$16/$J$14+10^J31*$J$19/$J$14))</f>
+        <v>0.99944605230987316</v>
+      </c>
+      <c r="L31" s="104">
+        <f>IF(D31=0,"",1/(1+10^I31/10^J31*$J$13/$J$19))</f>
+        <v>2.6298595708697519E-4</v>
+      </c>
+      <c r="M31" s="104">
+        <f>IF(D31=0,"",1-L31)</f>
+        <v>0.99973701404291304</v>
+      </c>
+      <c r="N31" s="104">
+        <f>IF(D31=0,"",1/(1/10^E31*$J$20/$J$22+10^D31/10^E31*$J$21/$J$22+10^I31/10^E31*$J$13/$J$22+1))</f>
+        <v>2.0699225912179477E-8</v>
+      </c>
+      <c r="O31" s="105">
+        <f>IF(D31=0,"",F31*K31*$J$7/$J$14)</f>
+        <v>3.167325197466116E-4</v>
+      </c>
+      <c r="P31" s="105">
+        <f>IF(D31=0,"",O31*10^J31)</f>
+        <v>3.0096790817650835E-4</v>
+      </c>
+      <c r="Q31" s="105">
+        <f>IF(D31=0,"",F31*N31*$J$7/$J$22)</f>
+        <v>5.1497234108152193E-6</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="10"/>
+        <v>1.0023181004639607</v>
+      </c>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -15573,64 +15570,67 @@
       <c r="AE31" s="7"/>
       <c r="AF31" s="7"/>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A32" s="96" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="97" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="93" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" s="98">
-        <v>0.35</v>
-      </c>
-      <c r="E32" s="98">
-        <v>0.53</v>
-      </c>
-      <c r="F32" s="99">
-        <v>1.6899999999999999E-4</v>
-      </c>
-      <c r="G32" s="174"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="104">
-        <f t="shared" si="1"/>
-        <v>1.4856678969095052E-3</v>
-      </c>
-      <c r="J32" s="104">
-        <f t="shared" si="2"/>
-        <v>3.1269911385632183E-2</v>
-      </c>
-      <c r="K32" s="105">
-        <f t="shared" si="3"/>
-        <v>0.99370986963868468</v>
-      </c>
-      <c r="L32" s="105">
-        <f t="shared" si="4"/>
-        <v>2.9571624469205309E-4</v>
-      </c>
-      <c r="M32" s="105">
-        <f t="shared" si="5"/>
-        <v>0.99970428375530795</v>
-      </c>
-      <c r="N32" s="105">
-        <f t="shared" si="6"/>
-        <v>4.2890696890696657E-6</v>
-      </c>
-      <c r="O32" s="106">
-        <f t="shared" si="7"/>
-        <v>1.6841955835762709E-4</v>
-      </c>
-      <c r="P32" s="106">
-        <f t="shared" si="8"/>
-        <v>1.8099327378133442E-4</v>
-      </c>
-      <c r="Q32" s="106">
-        <f t="shared" si="9"/>
-        <v>5.7067983129027342E-4</v>
-      </c>
-      <c r="R32" s="9"/>
+        <v>87</v>
+      </c>
+      <c r="B32" s="95" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="190" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="191">
+        <v>0.54749180498968375</v>
+      </c>
+      <c r="E32" s="191">
+        <v>0.30136158174588817</v>
+      </c>
+      <c r="F32" s="192">
+        <v>4.1100000000000002E-4</v>
+      </c>
+      <c r="G32" s="143"/>
+      <c r="H32" s="143"/>
+      <c r="I32" s="103">
+        <f>IF(D32=0,"",LOG($K$15*10^D32+$K$16*10^E32+$K$14))</f>
+        <v>2.7088167279582099E-3</v>
+      </c>
+      <c r="J32" s="103">
+        <f>IF(D32=0,"",LOG($K$21*10^D32+$K$22*10^E32+$K$20))</f>
+        <v>5.4816318723719386E-2</v>
+      </c>
+      <c r="K32" s="104">
+        <f>IF(D32=0,"",1/(1+10^D32*$J$15/$J$14+10^E32*$J$16/$J$14+10^J32*$J$19/$J$14))</f>
+        <v>0.99089966268504415</v>
+      </c>
+      <c r="L32" s="104">
+        <f>IF(D32=0,"",1/(1+10^I32/10^J32*$J$13/$J$19))</f>
+        <v>3.1130899330044921E-4</v>
+      </c>
+      <c r="M32" s="104">
+        <f>IF(D32=0,"",1-L32)</f>
+        <v>0.99968869100669955</v>
+      </c>
+      <c r="N32" s="104">
+        <f>IF(D32=0,"",1/(1/10^E32*$J$20/$J$22+10^D32/10^E32*$J$21/$J$22+10^I32/10^E32*$J$13/$J$22+1))</f>
+        <v>2.5263572382734385E-6</v>
+      </c>
+      <c r="O32" s="105">
+        <f>IF(D32=0,"",F32*K32*$J$7/$J$14)</f>
+        <v>4.0843007930433154E-4</v>
+      </c>
+      <c r="P32" s="105">
+        <f>IF(D32=0,"",O32*10^J32)</f>
+        <v>4.6337653471500517E-4</v>
+      </c>
+      <c r="Q32" s="105">
+        <f>IF(D32=0,"",F32*N32*$J$7/$J$22)</f>
+        <v>8.1748407371320464E-4</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="10"/>
+        <v>0.99374715159204752</v>
+      </c>
       <c r="S32" s="7"/>
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
@@ -15646,64 +15646,67 @@
       <c r="AE32" s="7"/>
       <c r="AF32" s="7"/>
     </row>
-    <row r="33" spans="1:32">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="96" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="97" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="93" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" s="98">
-        <v>0.35</v>
-      </c>
-      <c r="E33" s="98">
-        <v>0.53</v>
-      </c>
-      <c r="F33" s="99">
-        <v>1.47E-4</v>
-      </c>
-      <c r="G33" s="174"/>
-      <c r="H33" s="174"/>
-      <c r="I33" s="104">
-        <f t="shared" si="1"/>
-        <v>1.4856678969095052E-3</v>
-      </c>
-      <c r="J33" s="104">
-        <f t="shared" si="2"/>
-        <v>3.1269911385632183E-2</v>
-      </c>
-      <c r="K33" s="105">
-        <f t="shared" si="3"/>
-        <v>0.99370986963868468</v>
-      </c>
-      <c r="L33" s="105">
-        <f t="shared" si="4"/>
-        <v>2.9571624469205309E-4</v>
-      </c>
-      <c r="M33" s="105">
-        <f t="shared" si="5"/>
-        <v>0.99970428375530795</v>
-      </c>
-      <c r="N33" s="105">
-        <f t="shared" si="6"/>
-        <v>4.2890696890696657E-6</v>
-      </c>
-      <c r="O33" s="106">
-        <f t="shared" si="7"/>
-        <v>1.4649511880811348E-4</v>
-      </c>
-      <c r="P33" s="106">
-        <f t="shared" si="8"/>
-        <v>1.5743201920624943E-4</v>
-      </c>
-      <c r="Q33" s="106">
-        <f t="shared" si="9"/>
-        <v>4.9639014911047449E-4</v>
-      </c>
-      <c r="R33" s="9"/>
+        <v>87</v>
+      </c>
+      <c r="B33" s="95" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="190" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="191">
+        <v>1.6452318246143236</v>
+      </c>
+      <c r="E33" s="191">
+        <v>1.8629354124795308</v>
+      </c>
+      <c r="F33" s="192">
+        <v>2.63E-4</v>
+      </c>
+      <c r="G33" s="143"/>
+      <c r="H33" s="143"/>
+      <c r="I33" s="103">
+        <f>IF(D33=0,"",LOG($K$15*10^D33+$K$16*10^E33+$K$14))</f>
+        <v>4.8170235728069784E-2</v>
+      </c>
+      <c r="J33" s="103">
+        <f>IF(D33=0,"",LOG($K$21*10^D33+$K$22*10^E33+$K$20))</f>
+        <v>0.55027539138021464</v>
+      </c>
+      <c r="K33" s="104">
+        <f>IF(D33=0,"",1/(1+10^D33*$J$15/$J$14+10^E33*$J$16/$J$14+10^J33*$J$19/$J$14))</f>
+        <v>0.89191298814208886</v>
+      </c>
+      <c r="L33" s="104">
+        <f>IF(D33=0,"",1/(1+10^I33/10^J33*$J$13/$J$19))</f>
+        <v>8.7688682982693634E-4</v>
+      </c>
+      <c r="M33" s="104">
+        <f>IF(D33=0,"",1-L33)</f>
+        <v>0.9991231131701731</v>
+      </c>
+      <c r="N33" s="104">
+        <f>IF(D33=0,"",1/(1/10^E33*$J$20/$J$22+10^D33/10^E33*$J$21/$J$22+10^I33/10^E33*$J$13/$J$22+1))</f>
+        <v>8.2863142630746172E-5</v>
+      </c>
+      <c r="O33" s="105">
+        <f>IF(D33=0,"",F33*K33*$J$7/$J$14)</f>
+        <v>2.3524719457016768E-4</v>
+      </c>
+      <c r="P33" s="105">
+        <f>IF(D33=0,"",O33*10^J33)</f>
+        <v>8.3521799807471215E-4</v>
+      </c>
+      <c r="Q33" s="105">
+        <f>IF(D33=0,"",F33*N33*$J$7/$J$22)</f>
+        <v>1.7157731426808768E-2</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="10"/>
+        <v>0.89447602498162615</v>
+      </c>
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
@@ -15719,64 +15722,67 @@
       <c r="AE33" s="7"/>
       <c r="AF33" s="7"/>
     </row>
-    <row r="34" spans="1:32">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A34" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="100" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="101" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="102">
-        <v>0.35</v>
-      </c>
-      <c r="E34" s="102">
-        <v>0.53</v>
-      </c>
-      <c r="F34" s="103">
-        <v>8.9400000000000005E-5</v>
-      </c>
-      <c r="G34" s="174"/>
-      <c r="H34" s="174"/>
-      <c r="I34" s="104">
-        <f t="shared" si="1"/>
-        <v>1.4856678969095052E-3</v>
-      </c>
-      <c r="J34" s="104">
-        <f t="shared" si="2"/>
-        <v>3.1269911385632183E-2</v>
-      </c>
-      <c r="K34" s="105">
-        <f t="shared" si="3"/>
-        <v>0.99370986963868468</v>
-      </c>
-      <c r="L34" s="105">
-        <f t="shared" si="4"/>
-        <v>2.9571624469205309E-4</v>
-      </c>
-      <c r="M34" s="105">
-        <f t="shared" si="5"/>
-        <v>0.99970428375530795</v>
-      </c>
-      <c r="N34" s="105">
-        <f t="shared" si="6"/>
-        <v>4.2890696890696657E-6</v>
-      </c>
-      <c r="O34" s="106">
-        <f t="shared" si="7"/>
-        <v>8.9092949805750672E-5</v>
-      </c>
-      <c r="P34" s="106">
-        <f t="shared" si="8"/>
-        <v>9.574437086420886E-5</v>
-      </c>
-      <c r="Q34" s="106">
-        <f t="shared" si="9"/>
-        <v>3.0188625394881924E-4</v>
-      </c>
-      <c r="R34" s="9"/>
+        <v>87</v>
+      </c>
+      <c r="B34" s="95" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="190" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="191">
+        <v>0.39857726844789648</v>
+      </c>
+      <c r="E34" s="191">
+        <v>8.9525410045599246E-2</v>
+      </c>
+      <c r="F34" s="192">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="G34" s="143"/>
+      <c r="H34" s="143"/>
+      <c r="I34" s="103">
+        <f>IF(D34=0,"",LOG($K$15*10^D34+$K$16*10^E34+$K$14))</f>
+        <v>1.5832869039701305E-3</v>
+      </c>
+      <c r="J34" s="103">
+        <f>IF(D34=0,"",LOG($K$21*10^D34+$K$22*10^E34+$K$20))</f>
+        <v>3.2756419092886777E-2</v>
+      </c>
+      <c r="K34" s="104">
+        <f>IF(D34=0,"",1/(1+10^D34*$J$15/$J$14+10^E34*$J$16/$J$14+10^J34*$J$19/$J$14))</f>
+        <v>0.99348559148643589</v>
+      </c>
+      <c r="L34" s="104">
+        <f>IF(D34=0,"",1/(1+10^I34/10^J34*$J$13/$J$19))</f>
+        <v>2.9666318823460733E-4</v>
+      </c>
+      <c r="M34" s="104">
+        <f>IF(D34=0,"",1-L34)</f>
+        <v>0.99970333681176538</v>
+      </c>
+      <c r="N34" s="104">
+        <f>IF(D34=0,"",1/(1/10^E34*$J$20/$J$22+10^D34/10^E34*$J$21/$J$22+10^I34/10^E34*$J$13/$J$22+1))</f>
+        <v>1.5552151648887873E-6</v>
+      </c>
+      <c r="O34" s="105">
+        <f>IF(D34=0,"",F34*K34*$J$7/$J$14)</f>
+        <v>1.0959745625640691E-3</v>
+      </c>
+      <c r="P34" s="105">
+        <f>IF(D34=0,"",O34*10^J34)</f>
+        <v>1.1818351251434937E-3</v>
+      </c>
+      <c r="Q34" s="105">
+        <f>IF(D34=0,"",F34*N34*$J$7/$J$22)</f>
+        <v>1.3468706350846494E-3</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="10"/>
+        <v>0.99634051142188096</v>
+      </c>
       <c r="S34" s="7"/>
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
@@ -15792,66 +15798,66 @@
       <c r="AE34" s="7"/>
       <c r="AF34" s="7"/>
     </row>
-    <row r="35" spans="1:32">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A35" s="94" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B35" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="93" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="98">
-        <v>2.3628240000000003</v>
-      </c>
-      <c r="E35" s="98">
-        <v>2.5674030000000005</v>
-      </c>
-      <c r="F35" s="99">
-        <v>3.1599999999999998E-4</v>
-      </c>
-      <c r="G35" s="174"/>
-      <c r="H35" s="174"/>
+      <c r="C35" s="190" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="191">
+        <v>0.27761205565007074</v>
+      </c>
+      <c r="E35" s="191">
+        <v>-8.2551864497786676E-2</v>
+      </c>
+      <c r="F35" s="192">
+        <v>2.1499999999999999E-4</v>
+      </c>
+      <c r="G35" s="143"/>
+      <c r="H35" s="143"/>
       <c r="I35" s="55">
-        <f t="shared" si="1"/>
-        <v>0.20977654237414306</v>
+        <f>IF(D35=0,"",LOG($K$15*10^D35+$K$16*10^E35+$K$14))</f>
+        <v>9.1762308695912469E-4</v>
       </c>
       <c r="J35" s="55">
-        <f t="shared" si="2"/>
-        <v>1.1612107058937788</v>
+        <f>IF(D35=0,"",LOG($K$21*10^D35+$K$22*10^E35+$K$20))</f>
+        <v>1.9202448718581972E-2</v>
       </c>
       <c r="K35" s="56">
-        <f t="shared" si="3"/>
-        <v>0.61379860623581817</v>
+        <f>IF(D35=0,"",1/(1+10^D35*$J$15/$J$14+10^E35*$J$16/$J$14+10^J35*$J$19/$J$14))</f>
+        <v>0.9950181530617862</v>
       </c>
       <c r="L35" s="56">
-        <f t="shared" si="4"/>
-        <v>2.4636685048035098E-3</v>
+        <f>IF(D35=0,"",1/(1+10^I35/10^J35*$J$13/$J$19))</f>
+        <v>2.8799113573749083E-4</v>
       </c>
       <c r="M35" s="56">
-        <f t="shared" si="5"/>
-        <v>0.99753633149519649</v>
+        <f>IF(D35=0,"",1-L35)</f>
+        <v>0.99971200886426248</v>
       </c>
       <c r="N35" s="56">
-        <f t="shared" si="6"/>
-        <v>2.8875691771960597E-4</v>
+        <f>IF(D35=0,"",1/(1/10^E35*$J$20/$J$22+10^D35/10^E35*$J$21/$J$22+10^I35/10^E35*$J$13/$J$22+1))</f>
+        <v>1.0480515364860531E-6</v>
       </c>
       <c r="O35" s="57">
-        <f t="shared" si="7"/>
-        <v>1.945177318182584E-4</v>
+        <f>IF(D35=0,"",F35*K35*$J$7/$J$14)</f>
+        <v>2.1454365756090756E-4</v>
       </c>
       <c r="P35" s="57">
-        <f t="shared" si="8"/>
-        <v>2.8194857419167559E-3</v>
+        <f>IF(D35=0,"",O35*10^J35)</f>
+        <v>2.2424260450052869E-4</v>
       </c>
       <c r="Q35" s="57">
-        <f t="shared" si="9"/>
-        <v>7.1839317350535975E-2</v>
+        <f>IF(D35=0,"",F35*N35*$J$7/$J$22)</f>
+        <v>1.7740416663276608E-4</v>
       </c>
       <c r="R35" s="9">
         <f t="shared" si="10"/>
-        <v>0.61556244246284308</v>
+        <v>0.99787747702747709</v>
       </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
@@ -15868,67 +15874,54 @@
       <c r="AE35" s="7"/>
       <c r="AF35" s="7"/>
     </row>
-    <row r="36" spans="1:32">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A36" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="93" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" s="98">
-        <v>3.2672240000000001</v>
-      </c>
-      <c r="E36" s="98">
-        <v>3.6253630000000006</v>
-      </c>
-      <c r="F36" s="99">
-        <v>4.1100000000000002E-4</v>
-      </c>
-      <c r="G36" s="174"/>
-      <c r="H36" s="174"/>
-      <c r="I36" s="55">
-        <f t="shared" si="1"/>
-        <v>0.79517329783613067</v>
-      </c>
-      <c r="J36" s="55">
-        <f t="shared" si="2"/>
-        <v>2.0624304445312611</v>
-      </c>
-      <c r="K36" s="56">
-        <f t="shared" si="3"/>
-        <v>0.15903274074073803</v>
-      </c>
-      <c r="L36" s="56">
-        <f t="shared" si="4"/>
-        <v>5.0846686396126325E-3</v>
-      </c>
-      <c r="M36" s="56">
-        <f t="shared" si="5"/>
-        <v>0.99491533136038734</v>
-      </c>
-      <c r="N36" s="56">
-        <f t="shared" si="6"/>
-        <v>8.5497426593748264E-4</v>
-      </c>
-      <c r="O36" s="57">
-        <f t="shared" si="7"/>
-        <v>6.5550284613801786E-5</v>
-      </c>
-      <c r="P36" s="57">
-        <f t="shared" si="8"/>
-        <v>7.5684165414515872E-3</v>
-      </c>
-      <c r="Q36" s="57">
-        <f t="shared" si="9"/>
-        <v>0.27665439995975827</v>
-      </c>
-      <c r="R36" s="9">
-        <f t="shared" si="10"/>
-        <v>0.15948974358589241</v>
-      </c>
+      <c r="B36" s="95"/>
+      <c r="C36" s="190"/>
+      <c r="D36" s="191"/>
+      <c r="E36" s="191"/>
+      <c r="F36" s="192"/>
+      <c r="G36" s="143"/>
+      <c r="H36" s="143"/>
+      <c r="I36" s="55" t="str">
+        <f>IF(D36=0,"",LOG($K$15*10^D36+$K$16*10^E36+$K$14))</f>
+        <v/>
+      </c>
+      <c r="J36" s="55" t="str">
+        <f>IF(D36=0,"",LOG($K$21*10^D36+$K$22*10^E36+$K$20))</f>
+        <v/>
+      </c>
+      <c r="K36" s="56" t="str">
+        <f>IF(D36=0,"",1/(1+10^D36*$J$15/$J$14+10^E36*$J$16/$J$14+10^J36*$J$19/$J$14))</f>
+        <v/>
+      </c>
+      <c r="L36" s="56" t="str">
+        <f>IF(D36=0,"",1/(1+10^I36/10^J36*$J$13/$J$19))</f>
+        <v/>
+      </c>
+      <c r="M36" s="56" t="str">
+        <f>IF(D36=0,"",1-L36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="56" t="str">
+        <f>IF(D36=0,"",1/(1/10^E36*$J$20/$J$22+10^D36/10^E36*$J$21/$J$22+10^I36/10^E36*$J$13/$J$22+1))</f>
+        <v/>
+      </c>
+      <c r="O36" s="57" t="str">
+        <f>IF(D36=0,"",F36*K36*$J$7/$J$14)</f>
+        <v/>
+      </c>
+      <c r="P36" s="57" t="str">
+        <f>IF(D36=0,"",O36*10^J36)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="57" t="str">
+        <f>IF(D36=0,"",F36*N36*$J$7/$J$22)</f>
+        <v/>
+      </c>
+      <c r="R36" s="9"/>
       <c r="S36" s="7"/>
       <c r="T36" s="7"/>
       <c r="U36" s="7"/>
@@ -15944,67 +15937,54 @@
       <c r="AE36" s="7"/>
       <c r="AF36" s="7"/>
     </row>
-    <row r="37" spans="1:32">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A37" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="95" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" s="98">
-        <v>2.9091840000000002</v>
-      </c>
-      <c r="E37" s="98">
-        <v>3.4102429999999995</v>
-      </c>
-      <c r="F37" s="99">
-        <v>2.63E-4</v>
-      </c>
-      <c r="G37" s="174"/>
-      <c r="H37" s="174"/>
-      <c r="I37" s="55">
-        <f t="shared" si="1"/>
-        <v>0.53569782003481292</v>
-      </c>
-      <c r="J37" s="55">
-        <f t="shared" si="2"/>
-        <v>1.7362012296197693</v>
-      </c>
-      <c r="K37" s="56">
-        <f t="shared" si="3"/>
-        <v>0.28925225752812384</v>
-      </c>
-      <c r="L37" s="56">
-        <f t="shared" si="4"/>
-        <v>4.3633862079232501E-3</v>
-      </c>
-      <c r="M37" s="56">
-        <f t="shared" si="5"/>
-        <v>0.9956366137920768</v>
-      </c>
-      <c r="N37" s="56">
-        <f t="shared" si="6"/>
-        <v>9.4759608249004158E-4</v>
-      </c>
-      <c r="O37" s="57">
-        <f t="shared" si="7"/>
-        <v>7.6291951133397511E-5</v>
-      </c>
-      <c r="P37" s="57">
-        <f t="shared" si="8"/>
-        <v>4.1560422273963513E-3</v>
-      </c>
-      <c r="Q37" s="57">
-        <f t="shared" si="9"/>
-        <v>0.19621026391566695</v>
-      </c>
-      <c r="R37" s="9">
-        <f t="shared" si="10"/>
-        <v>0.29008346438554189</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B37" s="95"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="97"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="143"/>
+      <c r="H37" s="143"/>
+      <c r="I37" s="55" t="str">
+        <f>IF(D37=0,"",LOG($K$15*10^D37+$K$16*10^E37+$K$14))</f>
+        <v/>
+      </c>
+      <c r="J37" s="55" t="str">
+        <f>IF(D37=0,"",LOG($K$21*10^D37+$K$22*10^E37+$K$20))</f>
+        <v/>
+      </c>
+      <c r="K37" s="56" t="str">
+        <f>IF(D37=0,"",1/(1+10^D37*$J$15/$J$14+10^E37*$J$16/$J$14+10^J37*$J$19/$J$14))</f>
+        <v/>
+      </c>
+      <c r="L37" s="56" t="str">
+        <f>IF(D37=0,"",1/(1+10^I37/10^J37*$J$13/$J$19))</f>
+        <v/>
+      </c>
+      <c r="M37" s="56" t="str">
+        <f>IF(D37=0,"",1-L37)</f>
+        <v/>
+      </c>
+      <c r="N37" s="56" t="str">
+        <f>IF(D37=0,"",1/(1/10^E37*$J$20/$J$22+10^D37/10^E37*$J$21/$J$22+10^I37/10^E37*$J$13/$J$22+1))</f>
+        <v/>
+      </c>
+      <c r="O37" s="57" t="str">
+        <f>IF(D37=0,"",F37*K37*$J$7/$J$14)</f>
+        <v/>
+      </c>
+      <c r="P37" s="57" t="str">
+        <f>IF(D37=0,"",O37*10^J37)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="57" t="str">
+        <f>IF(D37=0,"",F37*N37*$J$7/$J$22)</f>
+        <v/>
+      </c>
+      <c r="R37" s="9"/>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
@@ -16020,67 +16000,54 @@
       <c r="AE37" s="7"/>
       <c r="AF37" s="7"/>
     </row>
-    <row r="38" spans="1:32">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A38" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="95" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" s="98">
-        <v>2.857424</v>
-      </c>
-      <c r="E38" s="98">
-        <v>3.3289280000000003</v>
-      </c>
-      <c r="F38" s="99">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="G38" s="174"/>
-      <c r="H38" s="174"/>
-      <c r="I38" s="55">
-        <f t="shared" si="1"/>
-        <v>0.49568105196432</v>
-      </c>
-      <c r="J38" s="55">
-        <f t="shared" si="2"/>
-        <v>1.6791568618493466</v>
-      </c>
-      <c r="K38" s="56">
-        <f t="shared" si="3"/>
-        <v>0.3172242590667107</v>
-      </c>
-      <c r="L38" s="56">
-        <f t="shared" si="4"/>
-        <v>4.1963231149935261E-3</v>
-      </c>
-      <c r="M38" s="56">
-        <f t="shared" si="5"/>
-        <v>0.99580367688500648</v>
-      </c>
-      <c r="N38" s="56">
-        <f t="shared" si="6"/>
-        <v>8.6178293732174882E-4</v>
-      </c>
-      <c r="O38" s="57">
-        <f t="shared" si="7"/>
-        <v>3.4994943212530321E-4</v>
-      </c>
-      <c r="P38" s="57">
-        <f t="shared" si="8"/>
-        <v>1.6717146752393632E-2</v>
-      </c>
-      <c r="Q38" s="57">
-        <f t="shared" si="9"/>
-        <v>0.74633411395436089</v>
-      </c>
-      <c r="R38" s="9">
-        <f t="shared" si="10"/>
-        <v>0.31813584738663925</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B38" s="95"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="98"/>
+      <c r="G38" s="143"/>
+      <c r="H38" s="143"/>
+      <c r="I38" s="55" t="str">
+        <f>IF(D38=0,"",LOG($K$15*10^D38+$K$16*10^E38+$K$14))</f>
+        <v/>
+      </c>
+      <c r="J38" s="55" t="str">
+        <f>IF(D38=0,"",LOG($K$21*10^D38+$K$22*10^E38+$K$20))</f>
+        <v/>
+      </c>
+      <c r="K38" s="56" t="str">
+        <f>IF(D38=0,"",1/(1+10^D38*$J$15/$J$14+10^E38*$J$16/$J$14+10^J38*$J$19/$J$14))</f>
+        <v/>
+      </c>
+      <c r="L38" s="56" t="str">
+        <f>IF(D38=0,"",1/(1+10^I38/10^J38*$J$13/$J$19))</f>
+        <v/>
+      </c>
+      <c r="M38" s="56" t="str">
+        <f>IF(D38=0,"",1-L38)</f>
+        <v/>
+      </c>
+      <c r="N38" s="56" t="str">
+        <f>IF(D38=0,"",1/(1/10^E38*$J$20/$J$22+10^D38/10^E38*$J$21/$J$22+10^I38/10^E38*$J$13/$J$22+1))</f>
+        <v/>
+      </c>
+      <c r="O38" s="57" t="str">
+        <f>IF(D38=0,"",F38*K38*$J$7/$J$14)</f>
+        <v/>
+      </c>
+      <c r="P38" s="57" t="str">
+        <f>IF(D38=0,"",O38*10^J38)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="57" t="str">
+        <f>IF(D38=0,"",F38*N38*$J$7/$J$22)</f>
+        <v/>
+      </c>
+      <c r="R38" s="9"/>
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
@@ -16096,67 +16063,54 @@
       <c r="AE38" s="7"/>
       <c r="AF38" s="7"/>
     </row>
-    <row r="39" spans="1:32">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A39" s="94" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="95" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" s="98">
-        <v>2.0783680000000002</v>
-      </c>
-      <c r="E39" s="98">
-        <v>2.5770209999999998</v>
-      </c>
-      <c r="F39" s="99">
-        <v>2.1499999999999999E-4</v>
-      </c>
-      <c r="G39" s="174"/>
-      <c r="H39" s="174"/>
-      <c r="I39" s="55">
-        <f t="shared" si="1"/>
-        <v>0.13245609937548125</v>
-      </c>
-      <c r="J39" s="55">
-        <f t="shared" si="2"/>
-        <v>0.9463233758836328</v>
-      </c>
-      <c r="K39" s="56">
-        <f t="shared" si="3"/>
-        <v>0.73390006344159109</v>
-      </c>
-      <c r="L39" s="56">
-        <f t="shared" si="4"/>
-        <v>1.7959984969713868E-3</v>
-      </c>
-      <c r="M39" s="56">
-        <f t="shared" si="5"/>
-        <v>0.99820400150302857</v>
-      </c>
-      <c r="N39" s="56">
-        <f t="shared" si="6"/>
-        <v>3.5298920543809097E-4</v>
-      </c>
-      <c r="O39" s="57">
-        <f t="shared" si="7"/>
-        <v>1.5824194102433015E-4</v>
-      </c>
-      <c r="P39" s="57">
-        <f t="shared" si="8"/>
-        <v>1.3984436694850326E-3</v>
-      </c>
-      <c r="Q39" s="57">
-        <f t="shared" si="9"/>
-        <v>5.9750645498853401E-2</v>
-      </c>
-      <c r="R39" s="9">
-        <f t="shared" si="10"/>
-        <v>0.73600902802014023</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B39" s="95"/>
+      <c r="C39" s="93"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="98"/>
+      <c r="G39" s="143"/>
+      <c r="H39" s="143"/>
+      <c r="I39" s="55" t="str">
+        <f>IF(D39=0,"",LOG($K$15*10^D39+$K$16*10^E39+$K$14))</f>
+        <v/>
+      </c>
+      <c r="J39" s="55" t="str">
+        <f>IF(D39=0,"",LOG($K$21*10^D39+$K$22*10^E39+$K$20))</f>
+        <v/>
+      </c>
+      <c r="K39" s="56" t="str">
+        <f>IF(D39=0,"",1/(1+10^D39*$J$15/$J$14+10^E39*$J$16/$J$14+10^J39*$J$19/$J$14))</f>
+        <v/>
+      </c>
+      <c r="L39" s="56" t="str">
+        <f>IF(D39=0,"",1/(1+10^I39/10^J39*$J$13/$J$19))</f>
+        <v/>
+      </c>
+      <c r="M39" s="56" t="str">
+        <f>IF(D39=0,"",1-L39)</f>
+        <v/>
+      </c>
+      <c r="N39" s="56" t="str">
+        <f>IF(D39=0,"",1/(1/10^E39*$J$20/$J$22+10^D39/10^E39*$J$21/$J$22+10^I39/10^E39*$J$13/$J$22+1))</f>
+        <v/>
+      </c>
+      <c r="O39" s="57" t="str">
+        <f>IF(D39=0,"",F39*K39*$J$7/$J$14)</f>
+        <v/>
+      </c>
+      <c r="P39" s="57" t="str">
+        <f>IF(D39=0,"",O39*10^J39)</f>
+        <v/>
+      </c>
+      <c r="Q39" s="57" t="str">
+        <f>IF(D39=0,"",F39*N39*$J$7/$J$22)</f>
+        <v/>
+      </c>
+      <c r="R39" s="9"/>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
@@ -16172,15 +16126,15 @@
       <c r="AE39" s="7"/>
       <c r="AF39" s="7"/>
     </row>
-    <row r="40" spans="1:32">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A40" s="94"/>
       <c r="B40" s="47"/>
       <c r="C40" s="93"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="174"/>
-      <c r="H40" s="174"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="98"/>
+      <c r="G40" s="143"/>
+      <c r="H40" s="143"/>
       <c r="I40" s="55" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16233,15 +16187,15 @@
       <c r="AE40" s="7"/>
       <c r="AF40" s="7"/>
     </row>
-    <row r="41" spans="1:32">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A41" s="94"/>
       <c r="B41" s="47"/>
       <c r="C41" s="93"/>
-      <c r="D41" s="98"/>
-      <c r="E41" s="98"/>
-      <c r="F41" s="99"/>
-      <c r="G41" s="174"/>
-      <c r="H41" s="174"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="97"/>
+      <c r="F41" s="98"/>
+      <c r="G41" s="143"/>
+      <c r="H41" s="143"/>
       <c r="I41" s="55" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16294,48 +16248,48 @@
       <c r="AE41" s="7"/>
       <c r="AF41" s="7"/>
     </row>
-    <row r="42" spans="1:32">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A42" s="96"/>
       <c r="B42" s="47"/>
       <c r="C42" s="93"/>
-      <c r="D42" s="98"/>
-      <c r="E42" s="98"/>
-      <c r="F42" s="99"/>
-      <c r="G42" s="174"/>
-      <c r="H42" s="174"/>
-      <c r="I42" s="104" t="str">
+      <c r="D42" s="97"/>
+      <c r="E42" s="97"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="143"/>
+      <c r="H42" s="143"/>
+      <c r="I42" s="103" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J42" s="104" t="str">
+      <c r="J42" s="103" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K42" s="105" t="str">
+      <c r="K42" s="104" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L42" s="105" t="str">
+      <c r="L42" s="104" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M42" s="105" t="str">
+      <c r="M42" s="104" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N42" s="105" t="str">
+      <c r="N42" s="104" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O42" s="106" t="str">
+      <c r="O42" s="105" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P42" s="106" t="str">
+      <c r="P42" s="105" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q42" s="106" t="str">
+      <c r="Q42" s="105" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -16355,48 +16309,48 @@
       <c r="AE42" s="7"/>
       <c r="AF42" s="7"/>
     </row>
-    <row r="43" spans="1:32">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A43" s="96"/>
       <c r="B43" s="47"/>
       <c r="C43" s="93"/>
-      <c r="D43" s="98"/>
-      <c r="E43" s="98"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="174"/>
-      <c r="H43" s="174"/>
-      <c r="I43" s="104" t="str">
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="98"/>
+      <c r="G43" s="143"/>
+      <c r="H43" s="143"/>
+      <c r="I43" s="103" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J43" s="104" t="str">
+      <c r="J43" s="103" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K43" s="105" t="str">
+      <c r="K43" s="104" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L43" s="105" t="str">
+      <c r="L43" s="104" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M43" s="105" t="str">
+      <c r="M43" s="104" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N43" s="105" t="str">
+      <c r="N43" s="104" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O43" s="106" t="str">
+      <c r="O43" s="105" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P43" s="106" t="str">
+      <c r="P43" s="105" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q43" s="106" t="str">
+      <c r="Q43" s="105" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -16416,48 +16370,48 @@
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
     </row>
-    <row r="44" spans="1:32">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A44" s="96"/>
       <c r="B44" s="47"/>
       <c r="C44" s="93"/>
-      <c r="D44" s="98"/>
-      <c r="E44" s="98"/>
-      <c r="F44" s="99"/>
-      <c r="G44" s="174"/>
-      <c r="H44" s="174"/>
-      <c r="I44" s="104" t="str">
+      <c r="D44" s="97"/>
+      <c r="E44" s="97"/>
+      <c r="F44" s="98"/>
+      <c r="G44" s="143"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="103" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J44" s="104" t="str">
+      <c r="J44" s="103" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K44" s="105" t="str">
+      <c r="K44" s="104" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L44" s="105" t="str">
+      <c r="L44" s="104" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M44" s="105" t="str">
+      <c r="M44" s="104" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N44" s="105" t="str">
+      <c r="N44" s="104" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O44" s="106" t="str">
+      <c r="O44" s="105" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P44" s="106" t="str">
+      <c r="P44" s="105" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q44" s="106" t="str">
+      <c r="Q44" s="105" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -16477,48 +16431,48 @@
       <c r="AE44" s="7"/>
       <c r="AF44" s="7"/>
     </row>
-    <row r="45" spans="1:32">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A45" s="96"/>
       <c r="B45" s="47"/>
       <c r="C45" s="93"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="174"/>
-      <c r="H45" s="174"/>
-      <c r="I45" s="104" t="str">
+      <c r="D45" s="97"/>
+      <c r="E45" s="97"/>
+      <c r="F45" s="98"/>
+      <c r="G45" s="143"/>
+      <c r="H45" s="143"/>
+      <c r="I45" s="103" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J45" s="104" t="str">
+      <c r="J45" s="103" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K45" s="105" t="str">
+      <c r="K45" s="104" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L45" s="105" t="str">
+      <c r="L45" s="104" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M45" s="105" t="str">
+      <c r="M45" s="104" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N45" s="105" t="str">
+      <c r="N45" s="104" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O45" s="106" t="str">
+      <c r="O45" s="105" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P45" s="106" t="str">
+      <c r="P45" s="105" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q45" s="106" t="str">
+      <c r="Q45" s="105" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -16538,48 +16492,48 @@
       <c r="AE45" s="7"/>
       <c r="AF45" s="7"/>
     </row>
-    <row r="46" spans="1:32">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A46" s="94"/>
       <c r="B46" s="47"/>
-      <c r="C46" s="101"/>
-      <c r="D46" s="102"/>
-      <c r="E46" s="102"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="174"/>
-      <c r="H46" s="174"/>
-      <c r="I46" s="104" t="str">
+      <c r="C46" s="100"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="101"/>
+      <c r="F46" s="102"/>
+      <c r="G46" s="143"/>
+      <c r="H46" s="143"/>
+      <c r="I46" s="103" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J46" s="104" t="str">
+      <c r="J46" s="103" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K46" s="105" t="str">
+      <c r="K46" s="104" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L46" s="105" t="str">
+      <c r="L46" s="104" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M46" s="105" t="str">
+      <c r="M46" s="104" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N46" s="105" t="str">
+      <c r="N46" s="104" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O46" s="106" t="str">
+      <c r="O46" s="105" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P46" s="106" t="str">
+      <c r="P46" s="105" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q46" s="106" t="str">
+      <c r="Q46" s="105" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -16599,15 +16553,15 @@
       <c r="AE46" s="7"/>
       <c r="AF46" s="7"/>
     </row>
-    <row r="47" spans="1:32">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A47" s="94"/>
       <c r="B47" s="47"/>
       <c r="C47" s="93"/>
-      <c r="D47" s="98"/>
-      <c r="E47" s="98"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="174"/>
-      <c r="H47" s="174"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="98"/>
+      <c r="G47" s="143"/>
+      <c r="H47" s="143"/>
       <c r="I47" s="55" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -16660,15 +16614,15 @@
       <c r="AE47" s="7"/>
       <c r="AF47" s="7"/>
     </row>
-    <row r="48" spans="1:32">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A48" s="94"/>
       <c r="B48" s="47"/>
       <c r="C48" s="93"/>
-      <c r="D48" s="98"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="174"/>
-      <c r="H48" s="174"/>
+      <c r="D48" s="97"/>
+      <c r="E48" s="97"/>
+      <c r="F48" s="98"/>
+      <c r="G48" s="143"/>
+      <c r="H48" s="143"/>
       <c r="I48" s="55" t="str">
         <f t="shared" ref="I48:I50" si="11">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
         <v/>
@@ -16721,15 +16675,15 @@
       <c r="AE48" s="7"/>
       <c r="AF48" s="7"/>
     </row>
-    <row r="49" spans="1:32">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A49" s="94"/>
       <c r="B49" s="47"/>
       <c r="C49" s="93"/>
-      <c r="D49" s="98"/>
-      <c r="E49" s="98"/>
-      <c r="F49" s="99"/>
-      <c r="G49" s="174"/>
-      <c r="H49" s="174"/>
+      <c r="D49" s="97"/>
+      <c r="E49" s="97"/>
+      <c r="F49" s="98"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="143"/>
       <c r="I49" s="55" t="str">
         <f t="shared" si="11"/>
         <v/>
@@ -16782,15 +16736,15 @@
       <c r="AE49" s="7"/>
       <c r="AF49" s="7"/>
     </row>
-    <row r="50" spans="1:32">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A50" s="94"/>
       <c r="B50" s="47"/>
       <c r="C50" s="93"/>
-      <c r="D50" s="98"/>
-      <c r="E50" s="98"/>
-      <c r="F50" s="99"/>
-      <c r="G50" s="174"/>
-      <c r="H50" s="174"/>
+      <c r="D50" s="97"/>
+      <c r="E50" s="97"/>
+      <c r="F50" s="98"/>
+      <c r="G50" s="143"/>
+      <c r="H50" s="143"/>
       <c r="I50" s="55" t="str">
         <f t="shared" si="11"/>
         <v/>
@@ -16843,15 +16797,15 @@
       <c r="AE50" s="7"/>
       <c r="AF50" s="7"/>
     </row>
-    <row r="51" spans="1:32">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A51" s="94"/>
       <c r="B51" s="47"/>
       <c r="C51" s="93"/>
-      <c r="D51" s="98"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="99"/>
-      <c r="G51" s="174"/>
-      <c r="H51" s="174"/>
+      <c r="D51" s="97"/>
+      <c r="E51" s="97"/>
+      <c r="F51" s="98"/>
+      <c r="G51" s="143"/>
+      <c r="H51" s="143"/>
       <c r="I51" s="55" t="str">
         <f t="shared" ref="I51:I70" si="20">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
         <v/>
@@ -16904,15 +16858,15 @@
       <c r="AE51" s="7"/>
       <c r="AF51" s="7"/>
     </row>
-    <row r="52" spans="1:32">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A52" s="7"/>
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
       <c r="D52" s="48"/>
       <c r="E52" s="48"/>
       <c r="F52" s="58"/>
-      <c r="G52" s="174"/>
-      <c r="H52" s="174"/>
+      <c r="G52" s="143"/>
+      <c r="H52" s="143"/>
       <c r="I52" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -16965,15 +16919,15 @@
       <c r="AE52" s="7"/>
       <c r="AF52" s="7"/>
     </row>
-    <row r="53" spans="1:32">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A53" s="7"/>
       <c r="B53" s="47"/>
       <c r="C53" s="47"/>
       <c r="D53" s="48"/>
       <c r="E53" s="48"/>
       <c r="F53" s="58"/>
-      <c r="G53" s="174"/>
-      <c r="H53" s="174"/>
+      <c r="G53" s="143"/>
+      <c r="H53" s="143"/>
       <c r="I53" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17026,15 +16980,15 @@
       <c r="AE53" s="7"/>
       <c r="AF53" s="7"/>
     </row>
-    <row r="54" spans="1:32">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A54" s="7"/>
       <c r="B54" s="47"/>
       <c r="C54" s="47"/>
       <c r="D54" s="48"/>
       <c r="E54" s="48"/>
       <c r="F54" s="58"/>
-      <c r="G54" s="174"/>
-      <c r="H54" s="174"/>
+      <c r="G54" s="143"/>
+      <c r="H54" s="143"/>
       <c r="I54" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17087,15 +17041,15 @@
       <c r="AE54" s="7"/>
       <c r="AF54" s="7"/>
     </row>
-    <row r="55" spans="1:32">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A55" s="7"/>
       <c r="B55" s="47"/>
       <c r="C55" s="47"/>
       <c r="D55" s="48"/>
       <c r="E55" s="48"/>
       <c r="F55" s="58"/>
-      <c r="G55" s="174"/>
-      <c r="H55" s="174"/>
+      <c r="G55" s="143"/>
+      <c r="H55" s="143"/>
       <c r="I55" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17148,15 +17102,15 @@
       <c r="AE55" s="7"/>
       <c r="AF55" s="7"/>
     </row>
-    <row r="56" spans="1:32">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A56" s="7"/>
       <c r="B56" s="47"/>
       <c r="C56" s="47"/>
       <c r="D56" s="48"/>
       <c r="E56" s="48"/>
       <c r="F56" s="58"/>
-      <c r="G56" s="174"/>
-      <c r="H56" s="174"/>
+      <c r="G56" s="143"/>
+      <c r="H56" s="143"/>
       <c r="I56" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17209,15 +17163,15 @@
       <c r="AE56" s="7"/>
       <c r="AF56" s="7"/>
     </row>
-    <row r="57" spans="1:32">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A57" s="7"/>
       <c r="B57" s="92"/>
       <c r="C57" s="92"/>
-      <c r="D57" s="98"/>
-      <c r="E57" s="98"/>
-      <c r="F57" s="99"/>
-      <c r="G57" s="174"/>
-      <c r="H57" s="174"/>
+      <c r="D57" s="97"/>
+      <c r="E57" s="97"/>
+      <c r="F57" s="98"/>
+      <c r="G57" s="143"/>
+      <c r="H57" s="143"/>
       <c r="I57" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17270,15 +17224,15 @@
       <c r="AE57" s="7"/>
       <c r="AF57" s="7"/>
     </row>
-    <row r="58" spans="1:32">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A58" s="7"/>
       <c r="B58" s="47"/>
       <c r="C58" s="47"/>
       <c r="D58" s="48"/>
       <c r="E58" s="48"/>
       <c r="F58" s="58"/>
-      <c r="G58" s="174"/>
-      <c r="H58" s="174"/>
+      <c r="G58" s="143"/>
+      <c r="H58" s="143"/>
       <c r="I58" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17331,15 +17285,15 @@
       <c r="AE58" s="7"/>
       <c r="AF58" s="7"/>
     </row>
-    <row r="59" spans="1:32">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A59" s="7"/>
       <c r="B59" s="47"/>
       <c r="C59" s="47"/>
       <c r="D59" s="48"/>
       <c r="E59" s="48"/>
       <c r="F59" s="58"/>
-      <c r="G59" s="174"/>
-      <c r="H59" s="174"/>
+      <c r="G59" s="143"/>
+      <c r="H59" s="143"/>
       <c r="I59" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17392,15 +17346,15 @@
       <c r="AE59" s="7"/>
       <c r="AF59" s="7"/>
     </row>
-    <row r="60" spans="1:32">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A60" s="7"/>
       <c r="B60" s="47"/>
       <c r="C60" s="47"/>
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
       <c r="F60" s="58"/>
-      <c r="G60" s="174"/>
-      <c r="H60" s="174"/>
+      <c r="G60" s="143"/>
+      <c r="H60" s="143"/>
       <c r="I60" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17453,15 +17407,15 @@
       <c r="AE60" s="7"/>
       <c r="AF60" s="7"/>
     </row>
-    <row r="61" spans="1:32">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A61" s="7"/>
       <c r="B61" s="47"/>
       <c r="C61" s="47"/>
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="58"/>
-      <c r="G61" s="174"/>
-      <c r="H61" s="174"/>
+      <c r="G61" s="143"/>
+      <c r="H61" s="143"/>
       <c r="I61" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17514,15 +17468,15 @@
       <c r="AE61" s="7"/>
       <c r="AF61" s="7"/>
     </row>
-    <row r="62" spans="1:32">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A62" s="7"/>
       <c r="B62" s="47"/>
       <c r="C62" s="47"/>
       <c r="D62" s="48"/>
       <c r="E62" s="48"/>
       <c r="F62" s="58"/>
-      <c r="G62" s="174"/>
-      <c r="H62" s="174"/>
+      <c r="G62" s="143"/>
+      <c r="H62" s="143"/>
       <c r="I62" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17575,15 +17529,15 @@
       <c r="AE62" s="7"/>
       <c r="AF62" s="7"/>
     </row>
-    <row r="63" spans="1:32">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A63" s="7"/>
       <c r="B63" s="47"/>
       <c r="C63" s="47"/>
       <c r="D63" s="48"/>
       <c r="E63" s="48"/>
       <c r="F63" s="58"/>
-      <c r="G63" s="174"/>
-      <c r="H63" s="174"/>
+      <c r="G63" s="143"/>
+      <c r="H63" s="143"/>
       <c r="I63" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17636,15 +17590,15 @@
       <c r="AE63" s="7"/>
       <c r="AF63" s="7"/>
     </row>
-    <row r="64" spans="1:32">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A64" s="7"/>
       <c r="B64" s="47"/>
       <c r="C64" s="47"/>
       <c r="D64" s="48"/>
       <c r="E64" s="48"/>
       <c r="F64" s="58"/>
-      <c r="G64" s="174"/>
-      <c r="H64" s="174"/>
+      <c r="G64" s="143"/>
+      <c r="H64" s="143"/>
       <c r="I64" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17697,15 +17651,15 @@
       <c r="AE64" s="7"/>
       <c r="AF64" s="7"/>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A65" s="7"/>
       <c r="B65" s="47"/>
       <c r="C65" s="47"/>
       <c r="D65" s="48"/>
       <c r="E65" s="48"/>
       <c r="F65" s="58"/>
-      <c r="G65" s="174"/>
-      <c r="H65" s="174"/>
+      <c r="G65" s="143"/>
+      <c r="H65" s="143"/>
       <c r="I65" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17758,15 +17712,15 @@
       <c r="AE65" s="7"/>
       <c r="AF65" s="7"/>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A66" s="7"/>
       <c r="B66" s="47"/>
       <c r="C66" s="47"/>
       <c r="D66" s="48"/>
       <c r="E66" s="48"/>
       <c r="F66" s="58"/>
-      <c r="G66" s="174"/>
-      <c r="H66" s="174"/>
+      <c r="G66" s="143"/>
+      <c r="H66" s="143"/>
       <c r="I66" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17819,15 +17773,15 @@
       <c r="AE66" s="7"/>
       <c r="AF66" s="7"/>
     </row>
-    <row r="67" spans="1:32">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A67" s="7"/>
       <c r="B67" s="47"/>
       <c r="C67" s="47"/>
       <c r="D67" s="48"/>
       <c r="E67" s="48"/>
       <c r="F67" s="58"/>
-      <c r="G67" s="174"/>
-      <c r="H67" s="174"/>
+      <c r="G67" s="143"/>
+      <c r="H67" s="143"/>
       <c r="I67" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17880,15 +17834,15 @@
       <c r="AE67" s="7"/>
       <c r="AF67" s="7"/>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A68" s="7"/>
       <c r="B68" s="47"/>
       <c r="C68" s="47"/>
       <c r="D68" s="48"/>
       <c r="E68" s="48"/>
       <c r="F68" s="58"/>
-      <c r="G68" s="174"/>
-      <c r="H68" s="174"/>
+      <c r="G68" s="143"/>
+      <c r="H68" s="143"/>
       <c r="I68" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -17941,15 +17895,15 @@
       <c r="AE68" s="7"/>
       <c r="AF68" s="7"/>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A69" s="7"/>
       <c r="B69" s="47"/>
       <c r="C69" s="47"/>
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="174"/>
-      <c r="H69" s="174"/>
+      <c r="G69" s="143"/>
+      <c r="H69" s="143"/>
       <c r="I69" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -18002,15 +17956,15 @@
       <c r="AE69" s="7"/>
       <c r="AF69" s="7"/>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A70" s="7"/>
       <c r="B70" s="47"/>
       <c r="C70" s="47"/>
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70" s="58"/>
-      <c r="G70" s="174"/>
-      <c r="H70" s="174"/>
+      <c r="G70" s="143"/>
+      <c r="H70" s="143"/>
       <c r="I70" s="55" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -18063,15 +18017,15 @@
       <c r="AE70" s="7"/>
       <c r="AF70" s="7"/>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A71" s="7"/>
       <c r="B71" s="47"/>
       <c r="C71" s="47"/>
       <c r="D71" s="48"/>
       <c r="E71" s="48"/>
       <c r="F71" s="58"/>
-      <c r="G71" s="174"/>
-      <c r="H71" s="174"/>
+      <c r="G71" s="143"/>
+      <c r="H71" s="143"/>
       <c r="I71" s="55" t="str">
         <f t="shared" ref="I71:I122" si="29">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
         <v/>
@@ -18124,15 +18078,15 @@
       <c r="AE71" s="7"/>
       <c r="AF71" s="7"/>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A72" s="7"/>
       <c r="B72" s="47"/>
       <c r="C72" s="47"/>
       <c r="D72" s="48"/>
       <c r="E72" s="48"/>
       <c r="F72" s="58"/>
-      <c r="G72" s="174"/>
-      <c r="H72" s="174"/>
+      <c r="G72" s="143"/>
+      <c r="H72" s="143"/>
       <c r="I72" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18185,15 +18139,15 @@
       <c r="AE72" s="7"/>
       <c r="AF72" s="7"/>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A73" s="7"/>
       <c r="B73" s="47"/>
       <c r="C73" s="47"/>
       <c r="D73" s="48"/>
       <c r="E73" s="48"/>
       <c r="F73" s="58"/>
-      <c r="G73" s="174"/>
-      <c r="H73" s="174"/>
+      <c r="G73" s="143"/>
+      <c r="H73" s="143"/>
       <c r="I73" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18246,15 +18200,15 @@
       <c r="AE73" s="7"/>
       <c r="AF73" s="7"/>
     </row>
-    <row r="74" spans="1:32">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A74" s="7"/>
       <c r="B74" s="47"/>
       <c r="C74" s="47"/>
       <c r="D74" s="48"/>
       <c r="E74" s="48"/>
       <c r="F74" s="58"/>
-      <c r="G74" s="174"/>
-      <c r="H74" s="174"/>
+      <c r="G74" s="143"/>
+      <c r="H74" s="143"/>
       <c r="I74" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18307,15 +18261,15 @@
       <c r="AE74" s="7"/>
       <c r="AF74" s="7"/>
     </row>
-    <row r="75" spans="1:32">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A75" s="7"/>
       <c r="B75" s="47"/>
       <c r="C75" s="47"/>
       <c r="D75" s="48"/>
       <c r="E75" s="48"/>
       <c r="F75" s="58"/>
-      <c r="G75" s="174"/>
-      <c r="H75" s="174"/>
+      <c r="G75" s="143"/>
+      <c r="H75" s="143"/>
       <c r="I75" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18368,15 +18322,15 @@
       <c r="AE75" s="7"/>
       <c r="AF75" s="7"/>
     </row>
-    <row r="76" spans="1:32">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A76" s="7"/>
       <c r="B76" s="47"/>
       <c r="C76" s="47"/>
       <c r="D76" s="48"/>
       <c r="E76" s="48"/>
       <c r="F76" s="58"/>
-      <c r="G76" s="174"/>
-      <c r="H76" s="174"/>
+      <c r="G76" s="143"/>
+      <c r="H76" s="143"/>
       <c r="I76" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18429,15 +18383,15 @@
       <c r="AE76" s="7"/>
       <c r="AF76" s="7"/>
     </row>
-    <row r="77" spans="1:32">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A77" s="7"/>
       <c r="B77" s="47"/>
       <c r="C77" s="47"/>
       <c r="D77" s="48"/>
       <c r="E77" s="48"/>
       <c r="F77" s="58"/>
-      <c r="G77" s="174"/>
-      <c r="H77" s="174"/>
+      <c r="G77" s="143"/>
+      <c r="H77" s="143"/>
       <c r="I77" s="55" t="str">
         <f t="shared" si="29"/>
         <v/>
@@ -18490,7 +18444,7 @@
       <c r="AE77" s="7"/>
       <c r="AF77" s="7"/>
     </row>
-    <row r="78" spans="1:32">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A78" s="7"/>
       <c r="B78" s="47"/>
       <c r="C78" s="47"/>
@@ -18551,7 +18505,7 @@
       <c r="AE78" s="7"/>
       <c r="AF78" s="7"/>
     </row>
-    <row r="79" spans="1:32">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A79" s="7"/>
       <c r="B79" s="47"/>
       <c r="C79" s="47"/>
@@ -18612,7 +18566,7 @@
       <c r="AE79" s="7"/>
       <c r="AF79" s="7"/>
     </row>
-    <row r="80" spans="1:32">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A80" s="7"/>
       <c r="B80" s="47"/>
       <c r="C80" s="47"/>
@@ -18673,7 +18627,7 @@
       <c r="AE80" s="7"/>
       <c r="AF80" s="7"/>
     </row>
-    <row r="81" spans="1:32">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A81" s="7"/>
       <c r="B81" s="47"/>
       <c r="C81" s="47"/>
@@ -18734,7 +18688,7 @@
       <c r="AE81" s="7"/>
       <c r="AF81" s="7"/>
     </row>
-    <row r="82" spans="1:32">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A82" s="7"/>
       <c r="B82" s="47"/>
       <c r="C82" s="47"/>
@@ -18795,7 +18749,7 @@
       <c r="AE82" s="7"/>
       <c r="AF82" s="7"/>
     </row>
-    <row r="83" spans="1:32">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A83" s="7"/>
       <c r="B83" s="47"/>
       <c r="C83" s="47"/>
@@ -18856,7 +18810,7 @@
       <c r="AE83" s="7"/>
       <c r="AF83" s="7"/>
     </row>
-    <row r="84" spans="1:32">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A84" s="7"/>
       <c r="B84" s="47"/>
       <c r="C84" s="47"/>
@@ -18917,7 +18871,7 @@
       <c r="AE84" s="7"/>
       <c r="AF84" s="7"/>
     </row>
-    <row r="85" spans="1:32">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A85" s="7"/>
       <c r="B85" s="47"/>
       <c r="C85" s="47"/>
@@ -18978,7 +18932,7 @@
       <c r="AE85" s="7"/>
       <c r="AF85" s="7"/>
     </row>
-    <row r="86" spans="1:32">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A86" s="7"/>
       <c r="B86" s="47"/>
       <c r="C86" s="47"/>
@@ -19039,7 +18993,7 @@
       <c r="AE86" s="7"/>
       <c r="AF86" s="7"/>
     </row>
-    <row r="87" spans="1:32">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A87" s="7"/>
       <c r="B87" s="47"/>
       <c r="C87" s="47"/>
@@ -19100,7 +19054,7 @@
       <c r="AE87" s="7"/>
       <c r="AF87" s="7"/>
     </row>
-    <row r="88" spans="1:32">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A88" s="7"/>
       <c r="B88" s="47"/>
       <c r="C88" s="47"/>
@@ -19161,7 +19115,7 @@
       <c r="AE88" s="7"/>
       <c r="AF88" s="7"/>
     </row>
-    <row r="89" spans="1:32">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A89" s="7"/>
       <c r="B89" s="47"/>
       <c r="C89" s="47"/>
@@ -19222,7 +19176,7 @@
       <c r="AE89" s="7"/>
       <c r="AF89" s="7"/>
     </row>
-    <row r="90" spans="1:32">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A90" s="7"/>
       <c r="B90" s="47"/>
       <c r="C90" s="47"/>
@@ -19283,7 +19237,7 @@
       <c r="AE90" s="7"/>
       <c r="AF90" s="7"/>
     </row>
-    <row r="91" spans="1:32">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A91" s="7"/>
       <c r="B91" s="47"/>
       <c r="C91" s="47"/>
@@ -19344,7 +19298,7 @@
       <c r="AE91" s="7"/>
       <c r="AF91" s="7"/>
     </row>
-    <row r="92" spans="1:32">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A92" s="7"/>
       <c r="B92" s="47"/>
       <c r="C92" s="47"/>
@@ -19405,7 +19359,7 @@
       <c r="AE92" s="7"/>
       <c r="AF92" s="7"/>
     </row>
-    <row r="93" spans="1:32">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A93" s="7"/>
       <c r="B93" s="47"/>
       <c r="C93" s="47"/>
@@ -19466,7 +19420,7 @@
       <c r="AE93" s="7"/>
       <c r="AF93" s="7"/>
     </row>
-    <row r="94" spans="1:32">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A94" s="7"/>
       <c r="B94" s="47"/>
       <c r="C94" s="47"/>
@@ -19527,7 +19481,7 @@
       <c r="AE94" s="7"/>
       <c r="AF94" s="7"/>
     </row>
-    <row r="95" spans="1:32">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A95" s="7"/>
       <c r="B95" s="47"/>
       <c r="C95" s="47"/>
@@ -19588,7 +19542,7 @@
       <c r="AE95" s="7"/>
       <c r="AF95" s="7"/>
     </row>
-    <row r="96" spans="1:32">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A96" s="7"/>
       <c r="B96" s="47"/>
       <c r="C96" s="47"/>
@@ -19649,7 +19603,7 @@
       <c r="AE96" s="7"/>
       <c r="AF96" s="7"/>
     </row>
-    <row r="97" spans="1:32">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A97" s="7"/>
       <c r="B97" s="47"/>
       <c r="C97" s="47"/>
@@ -19710,7 +19664,7 @@
       <c r="AE97" s="7"/>
       <c r="AF97" s="7"/>
     </row>
-    <row r="98" spans="1:32">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A98" s="7"/>
       <c r="B98" s="47"/>
       <c r="C98" s="47"/>
@@ -19771,7 +19725,7 @@
       <c r="AE98" s="7"/>
       <c r="AF98" s="7"/>
     </row>
-    <row r="99" spans="1:32">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A99" s="7"/>
       <c r="B99" s="47"/>
       <c r="C99" s="47"/>
@@ -19832,7 +19786,7 @@
       <c r="AE99" s="7"/>
       <c r="AF99" s="7"/>
     </row>
-    <row r="100" spans="1:32">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A100" s="7"/>
       <c r="B100" s="47"/>
       <c r="C100" s="47"/>
@@ -19893,7 +19847,7 @@
       <c r="AE100" s="7"/>
       <c r="AF100" s="7"/>
     </row>
-    <row r="101" spans="1:32">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A101" s="7"/>
       <c r="B101" s="47"/>
       <c r="C101" s="47"/>
@@ -19954,7 +19908,7 @@
       <c r="AE101" s="7"/>
       <c r="AF101" s="7"/>
     </row>
-    <row r="102" spans="1:32">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A102" s="7"/>
       <c r="B102" s="47"/>
       <c r="C102" s="47"/>
@@ -20015,7 +19969,7 @@
       <c r="AE102" s="7"/>
       <c r="AF102" s="7"/>
     </row>
-    <row r="103" spans="1:32">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A103" s="7"/>
       <c r="B103" s="47"/>
       <c r="C103" s="47"/>
@@ -20076,7 +20030,7 @@
       <c r="AE103" s="7"/>
       <c r="AF103" s="7"/>
     </row>
-    <row r="104" spans="1:32">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A104" s="7"/>
       <c r="B104" s="47"/>
       <c r="C104" s="47"/>
@@ -20137,7 +20091,7 @@
       <c r="AE104" s="7"/>
       <c r="AF104" s="7"/>
     </row>
-    <row r="105" spans="1:32">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A105" s="7"/>
       <c r="B105" s="47"/>
       <c r="C105" s="47"/>
@@ -20198,7 +20152,7 @@
       <c r="AE105" s="7"/>
       <c r="AF105" s="7"/>
     </row>
-    <row r="106" spans="1:32">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A106" s="7"/>
       <c r="B106" s="47"/>
       <c r="C106" s="47"/>
@@ -20259,7 +20213,7 @@
       <c r="AE106" s="7"/>
       <c r="AF106" s="7"/>
     </row>
-    <row r="107" spans="1:32">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A107" s="7"/>
       <c r="B107" s="47"/>
       <c r="C107" s="47"/>
@@ -20320,7 +20274,7 @@
       <c r="AE107" s="7"/>
       <c r="AF107" s="7"/>
     </row>
-    <row r="108" spans="1:32">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A108" s="7"/>
       <c r="B108" s="47"/>
       <c r="C108" s="47"/>
@@ -20381,7 +20335,7 @@
       <c r="AE108" s="7"/>
       <c r="AF108" s="7"/>
     </row>
-    <row r="109" spans="1:32">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A109" s="7"/>
       <c r="B109" s="47"/>
       <c r="C109" s="47"/>
@@ -20442,7 +20396,7 @@
       <c r="AE109" s="7"/>
       <c r="AF109" s="7"/>
     </row>
-    <row r="110" spans="1:32">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A110" s="7"/>
       <c r="B110" s="47"/>
       <c r="C110" s="47"/>
@@ -20503,7 +20457,7 @@
       <c r="AE110" s="7"/>
       <c r="AF110" s="7"/>
     </row>
-    <row r="111" spans="1:32">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A111" s="7"/>
       <c r="B111" s="47"/>
       <c r="C111" s="47"/>
@@ -20564,7 +20518,7 @@
       <c r="AE111" s="7"/>
       <c r="AF111" s="7"/>
     </row>
-    <row r="112" spans="1:32">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A112" s="7"/>
       <c r="B112" s="47"/>
       <c r="C112" s="47"/>
@@ -20625,7 +20579,7 @@
       <c r="AE112" s="7"/>
       <c r="AF112" s="7"/>
     </row>
-    <row r="113" spans="1:32">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A113" s="7"/>
       <c r="B113" s="47"/>
       <c r="C113" s="47"/>
@@ -20686,7 +20640,7 @@
       <c r="AE113" s="7"/>
       <c r="AF113" s="7"/>
     </row>
-    <row r="114" spans="1:32">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A114" s="7"/>
       <c r="B114" s="47"/>
       <c r="C114" s="47"/>
@@ -20747,7 +20701,7 @@
       <c r="AE114" s="7"/>
       <c r="AF114" s="7"/>
     </row>
-    <row r="115" spans="1:32">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A115" s="7"/>
       <c r="B115" s="47"/>
       <c r="C115" s="47"/>
@@ -20808,7 +20762,7 @@
       <c r="AE115" s="7"/>
       <c r="AF115" s="7"/>
     </row>
-    <row r="116" spans="1:32">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A116" s="7"/>
       <c r="B116" s="47"/>
       <c r="C116" s="47"/>
@@ -20869,7 +20823,7 @@
       <c r="AE116" s="7"/>
       <c r="AF116" s="7"/>
     </row>
-    <row r="117" spans="1:32">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A117" s="7"/>
       <c r="B117" s="47"/>
       <c r="C117" s="47"/>
@@ -20930,7 +20884,7 @@
       <c r="AE117" s="7"/>
       <c r="AF117" s="7"/>
     </row>
-    <row r="118" spans="1:32">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A118" s="7"/>
       <c r="B118" s="47"/>
       <c r="C118" s="47"/>
@@ -20991,7 +20945,7 @@
       <c r="AE118" s="7"/>
       <c r="AF118" s="7"/>
     </row>
-    <row r="119" spans="1:32">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A119" s="7"/>
       <c r="B119" s="47"/>
       <c r="C119" s="47"/>
@@ -21052,7 +21006,7 @@
       <c r="AE119" s="7"/>
       <c r="AF119" s="7"/>
     </row>
-    <row r="120" spans="1:32">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A120" s="7"/>
       <c r="B120" s="47"/>
       <c r="C120" s="47"/>
@@ -21113,7 +21067,7 @@
       <c r="AE120" s="7"/>
       <c r="AF120" s="7"/>
     </row>
-    <row r="121" spans="1:32">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A121" s="7"/>
       <c r="B121" s="47"/>
       <c r="C121" s="47"/>
@@ -21174,7 +21128,7 @@
       <c r="AE121" s="7"/>
       <c r="AF121" s="7"/>
     </row>
-    <row r="122" spans="1:32">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A122" s="7"/>
       <c r="B122" s="47"/>
       <c r="C122" s="47"/>
@@ -21235,7 +21189,7 @@
       <c r="AE122" s="7"/>
       <c r="AF122" s="7"/>
     </row>
-    <row r="123" spans="1:32">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A123" s="7"/>
       <c r="B123" s="47"/>
       <c r="C123" s="47"/>
@@ -21296,7 +21250,7 @@
       <c r="AE123" s="7"/>
       <c r="AF123" s="7"/>
     </row>
-    <row r="124" spans="1:32">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A124" s="7"/>
       <c r="B124" s="47"/>
       <c r="C124" s="47"/>
@@ -21357,7 +21311,7 @@
       <c r="AE124" s="7"/>
       <c r="AF124" s="7"/>
     </row>
-    <row r="125" spans="1:32">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A125" s="7"/>
       <c r="B125" s="47"/>
       <c r="C125" s="47"/>
@@ -21418,7 +21372,7 @@
       <c r="AE125" s="7"/>
       <c r="AF125" s="7"/>
     </row>
-    <row r="126" spans="1:32">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A126" s="7"/>
       <c r="B126" s="47"/>
       <c r="C126" s="47"/>
@@ -21479,7 +21433,7 @@
       <c r="AE126" s="7"/>
       <c r="AF126" s="7"/>
     </row>
-    <row r="127" spans="1:32">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A127" s="7"/>
       <c r="B127" s="47"/>
       <c r="C127" s="47"/>
@@ -21540,7 +21494,7 @@
       <c r="AE127" s="7"/>
       <c r="AF127" s="7"/>
     </row>
-    <row r="128" spans="1:32">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A128" s="7"/>
       <c r="B128" s="82" t="s">
         <v>74</v>
@@ -21578,7 +21532,7 @@
       <c r="AE128" s="7"/>
       <c r="AF128" s="7"/>
     </row>
-    <row r="129" spans="1:32">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A129" s="7"/>
       <c r="B129" s="49"/>
       <c r="C129" s="49"/>
@@ -21612,7 +21566,7 @@
       <c r="AE129" s="7"/>
       <c r="AF129" s="7"/>
     </row>
-    <row r="130" spans="1:32">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A130" s="7"/>
       <c r="B130" s="49"/>
       <c r="C130" s="49"/>
@@ -21646,7 +21600,7 @@
       <c r="AE130" s="7"/>
       <c r="AF130" s="7"/>
     </row>
-    <row r="131" spans="1:32">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A131" s="7"/>
       <c r="B131" s="49"/>
       <c r="C131" s="49"/>
@@ -21680,7 +21634,7 @@
       <c r="AE131" s="7"/>
       <c r="AF131" s="7"/>
     </row>
-    <row r="132" spans="1:32">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A132" s="7"/>
       <c r="B132" s="49"/>
       <c r="C132" s="49"/>
@@ -21714,7 +21668,7 @@
       <c r="AE132" s="7"/>
       <c r="AF132" s="7"/>
     </row>
-    <row r="133" spans="1:32">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A133" s="7"/>
       <c r="B133" s="49"/>
       <c r="C133" s="49"/>
@@ -21748,7 +21702,7 @@
       <c r="AE133" s="7"/>
       <c r="AF133" s="7"/>
     </row>
-    <row r="134" spans="1:32">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A134" s="7"/>
       <c r="B134" s="49"/>
       <c r="C134" s="49"/>
@@ -21782,7 +21736,7 @@
       <c r="AE134" s="7"/>
       <c r="AF134" s="7"/>
     </row>
-    <row r="135" spans="1:32">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A135" s="7"/>
       <c r="B135" s="49"/>
       <c r="C135" s="49"/>
@@ -21816,7 +21770,7 @@
       <c r="AE135" s="7"/>
       <c r="AF135" s="7"/>
     </row>
-    <row r="136" spans="1:32">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A136" s="7"/>
       <c r="B136" s="49"/>
       <c r="C136" s="49"/>
@@ -21850,7 +21804,7 @@
       <c r="AE136" s="7"/>
       <c r="AF136" s="7"/>
     </row>
-    <row r="137" spans="1:32">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A137" s="7"/>
       <c r="B137" s="49"/>
       <c r="C137" s="49"/>
@@ -21884,7 +21838,7 @@
       <c r="AE137" s="7"/>
       <c r="AF137" s="7"/>
     </row>
-    <row r="138" spans="1:32">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A138" s="7"/>
       <c r="B138" s="49"/>
       <c r="C138" s="49"/>
@@ -21918,7 +21872,7 @@
       <c r="AE138" s="7"/>
       <c r="AF138" s="7"/>
     </row>
-    <row r="139" spans="1:32">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A139" s="7"/>
       <c r="B139" s="49"/>
       <c r="C139" s="49"/>
@@ -21952,7 +21906,7 @@
       <c r="AE139" s="7"/>
       <c r="AF139" s="7"/>
     </row>
-    <row r="140" spans="1:32">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A140" s="7"/>
       <c r="B140" s="49"/>
       <c r="C140" s="49"/>
@@ -21986,7 +21940,7 @@
       <c r="AE140" s="7"/>
       <c r="AF140" s="7"/>
     </row>
-    <row r="141" spans="1:32">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A141" s="7"/>
       <c r="B141" s="49"/>
       <c r="C141" s="49"/>
@@ -22020,7 +21974,7 @@
       <c r="AE141" s="7"/>
       <c r="AF141" s="7"/>
     </row>
-    <row r="142" spans="1:32">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A142" s="7"/>
       <c r="B142" s="49"/>
       <c r="C142" s="49"/>
@@ -22054,7 +22008,7 @@
       <c r="AE142" s="7"/>
       <c r="AF142" s="7"/>
     </row>
-    <row r="143" spans="1:32">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A143" s="7"/>
       <c r="B143" s="49"/>
       <c r="C143" s="49"/>
@@ -22088,7 +22042,7 @@
       <c r="AE143" s="7"/>
       <c r="AF143" s="7"/>
     </row>
-    <row r="144" spans="1:32">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A144" s="7"/>
       <c r="B144" s="49"/>
       <c r="C144" s="49"/>
@@ -22122,7 +22076,7 @@
       <c r="AE144" s="7"/>
       <c r="AF144" s="7"/>
     </row>
-    <row r="145" spans="1:32">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A145" s="7"/>
       <c r="B145" s="49"/>
       <c r="C145" s="49"/>
@@ -22156,7 +22110,7 @@
       <c r="AE145" s="7"/>
       <c r="AF145" s="7"/>
     </row>
-    <row r="146" spans="1:32">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A146" s="7"/>
       <c r="B146" s="49"/>
       <c r="C146" s="49"/>
@@ -22190,7 +22144,7 @@
       <c r="AE146" s="7"/>
       <c r="AF146" s="7"/>
     </row>
-    <row r="147" spans="1:32">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A147" s="7"/>
       <c r="B147" s="49"/>
       <c r="C147" s="49"/>
@@ -22224,7 +22178,7 @@
       <c r="AE147" s="7"/>
       <c r="AF147" s="7"/>
     </row>
-    <row r="148" spans="1:32">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A148" s="7"/>
       <c r="B148" s="49"/>
       <c r="C148" s="49"/>
@@ -22258,7 +22212,7 @@
       <c r="AE148" s="7"/>
       <c r="AF148" s="7"/>
     </row>
-    <row r="149" spans="1:32">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A149" s="7"/>
       <c r="B149" s="49"/>
       <c r="C149" s="49"/>
@@ -22292,7 +22246,7 @@
       <c r="AE149" s="7"/>
       <c r="AF149" s="7"/>
     </row>
-    <row r="150" spans="1:32">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A150" s="7"/>
       <c r="B150" s="49"/>
       <c r="C150" s="49"/>
@@ -22326,7 +22280,7 @@
       <c r="AE150" s="7"/>
       <c r="AF150" s="7"/>
     </row>
-    <row r="151" spans="1:32">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A151" s="7"/>
       <c r="B151" s="49"/>
       <c r="C151" s="49"/>
@@ -22360,7 +22314,7 @@
       <c r="AE151" s="7"/>
       <c r="AF151" s="7"/>
     </row>
-    <row r="152" spans="1:32">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A152" s="7"/>
       <c r="B152" s="49"/>
       <c r="C152" s="49"/>
@@ -22394,7 +22348,7 @@
       <c r="AE152" s="7"/>
       <c r="AF152" s="7"/>
     </row>
-    <row r="153" spans="1:32">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A153" s="7"/>
       <c r="B153" s="49"/>
       <c r="C153" s="49"/>
@@ -22428,7 +22382,7 @@
       <c r="AE153" s="7"/>
       <c r="AF153" s="7"/>
     </row>
-    <row r="154" spans="1:32">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A154" s="7"/>
       <c r="B154" s="49"/>
       <c r="C154" s="49"/>
@@ -22462,7 +22416,7 @@
       <c r="AE154" s="7"/>
       <c r="AF154" s="7"/>
     </row>
-    <row r="155" spans="1:32">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A155" s="7"/>
       <c r="B155" s="49"/>
       <c r="C155" s="49"/>
@@ -22496,7 +22450,7 @@
       <c r="AE155" s="7"/>
       <c r="AF155" s="7"/>
     </row>
-    <row r="156" spans="1:32">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A156" s="7"/>
       <c r="B156" s="49"/>
       <c r="C156" s="49"/>
@@ -22530,7 +22484,7 @@
       <c r="AE156" s="7"/>
       <c r="AF156" s="7"/>
     </row>
-    <row r="157" spans="1:32">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A157" s="7"/>
       <c r="B157" s="49"/>
       <c r="C157" s="49"/>
@@ -22564,7 +22518,7 @@
       <c r="AE157" s="7"/>
       <c r="AF157" s="7"/>
     </row>
-    <row r="158" spans="1:32">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A158" s="7"/>
       <c r="B158" s="49"/>
       <c r="C158" s="49"/>
@@ -22598,7 +22552,7 @@
       <c r="AE158" s="7"/>
       <c r="AF158" s="7"/>
     </row>
-    <row r="159" spans="1:32">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A159" s="7"/>
       <c r="B159" s="49"/>
       <c r="C159" s="49"/>
@@ -22632,7 +22586,7 @@
       <c r="AE159" s="7"/>
       <c r="AF159" s="7"/>
     </row>
-    <row r="160" spans="1:32">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A160" s="7"/>
       <c r="B160" s="49"/>
       <c r="C160" s="49"/>
@@ -22666,7 +22620,7 @@
       <c r="AE160" s="7"/>
       <c r="AF160" s="7"/>
     </row>
-    <row r="161" spans="1:32">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A161" s="7"/>
       <c r="B161" s="49"/>
       <c r="C161" s="49"/>
@@ -22700,7 +22654,7 @@
       <c r="AE161" s="7"/>
       <c r="AF161" s="7"/>
     </row>
-    <row r="162" spans="1:32">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A162" s="7"/>
       <c r="B162" s="49"/>
       <c r="C162" s="49"/>
@@ -22734,7 +22688,7 @@
       <c r="AE162" s="7"/>
       <c r="AF162" s="7"/>
     </row>
-    <row r="163" spans="1:32">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A163" s="7"/>
       <c r="B163" s="49"/>
       <c r="C163" s="49"/>
@@ -22768,7 +22722,7 @@
       <c r="AE163" s="7"/>
       <c r="AF163" s="7"/>
     </row>
-    <row r="164" spans="1:32">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A164" s="7"/>
       <c r="B164" s="49"/>
       <c r="C164" s="49"/>
@@ -22802,7 +22756,7 @@
       <c r="AE164" s="7"/>
       <c r="AF164" s="7"/>
     </row>
-    <row r="165" spans="1:32">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A165" s="7"/>
       <c r="B165" s="49"/>
       <c r="C165" s="49"/>
@@ -22836,7 +22790,7 @@
       <c r="AE165" s="7"/>
       <c r="AF165" s="7"/>
     </row>
-    <row r="166" spans="1:32">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A166" s="7"/>
       <c r="B166" s="49"/>
       <c r="C166" s="49"/>
@@ -22870,7 +22824,7 @@
       <c r="AE166" s="7"/>
       <c r="AF166" s="7"/>
     </row>
-    <row r="167" spans="1:32">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A167" s="7"/>
       <c r="B167" s="49"/>
       <c r="C167" s="49"/>
@@ -22904,7 +22858,7 @@
       <c r="AE167" s="7"/>
       <c r="AF167" s="7"/>
     </row>
-    <row r="168" spans="1:32">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A168" s="7"/>
       <c r="B168" s="49"/>
       <c r="C168" s="49"/>
@@ -22938,7 +22892,7 @@
       <c r="AE168" s="7"/>
       <c r="AF168" s="7"/>
     </row>
-    <row r="169" spans="1:32">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A169" s="7"/>
       <c r="B169" s="49"/>
       <c r="C169" s="49"/>
@@ -22972,7 +22926,7 @@
       <c r="AE169" s="7"/>
       <c r="AF169" s="7"/>
     </row>
-    <row r="170" spans="1:32">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A170" s="7"/>
       <c r="B170" s="49"/>
       <c r="C170" s="49"/>
@@ -23006,7 +22960,7 @@
       <c r="AE170" s="7"/>
       <c r="AF170" s="7"/>
     </row>
-    <row r="171" spans="1:32">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A171" s="7"/>
       <c r="B171" s="49"/>
       <c r="C171" s="49"/>
@@ -23040,7 +22994,7 @@
       <c r="AE171" s="7"/>
       <c r="AF171" s="7"/>
     </row>
-    <row r="172" spans="1:32">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A172" s="7"/>
       <c r="B172" s="49"/>
       <c r="C172" s="49"/>
@@ -23074,7 +23028,7 @@
       <c r="AE172" s="7"/>
       <c r="AF172" s="7"/>
     </row>
-    <row r="173" spans="1:32">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A173" s="7"/>
       <c r="B173" s="49"/>
       <c r="C173" s="49"/>
@@ -23108,7 +23062,7 @@
       <c r="AE173" s="7"/>
       <c r="AF173" s="7"/>
     </row>
-    <row r="174" spans="1:32">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A174" s="7"/>
       <c r="B174" s="49"/>
       <c r="C174" s="49"/>
@@ -23142,7 +23096,7 @@
       <c r="AE174" s="7"/>
       <c r="AF174" s="7"/>
     </row>
-    <row r="175" spans="1:32">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A175" s="7"/>
       <c r="B175" s="49"/>
       <c r="C175" s="49"/>
@@ -23176,7 +23130,7 @@
       <c r="AE175" s="7"/>
       <c r="AF175" s="7"/>
     </row>
-    <row r="176" spans="1:32">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A176" s="7"/>
       <c r="B176" s="49"/>
       <c r="C176" s="49"/>
@@ -23210,7 +23164,7 @@
       <c r="AE176" s="7"/>
       <c r="AF176" s="7"/>
     </row>
-    <row r="177" spans="1:32">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A177" s="7"/>
       <c r="B177" s="49"/>
       <c r="C177" s="49"/>
@@ -23244,7 +23198,7 @@
       <c r="AE177" s="7"/>
       <c r="AF177" s="7"/>
     </row>
-    <row r="178" spans="1:32">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A178" s="7"/>
       <c r="B178" s="49"/>
       <c r="C178" s="49"/>
@@ -23278,7 +23232,7 @@
       <c r="AE178" s="7"/>
       <c r="AF178" s="7"/>
     </row>
-    <row r="179" spans="1:32">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A179" s="7"/>
       <c r="B179" s="49"/>
       <c r="C179" s="49"/>
@@ -23312,7 +23266,7 @@
       <c r="AE179" s="7"/>
       <c r="AF179" s="7"/>
     </row>
-    <row r="180" spans="1:32">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A180" s="7"/>
       <c r="B180" s="49"/>
       <c r="C180" s="49"/>
@@ -23346,7 +23300,7 @@
       <c r="AE180" s="7"/>
       <c r="AF180" s="7"/>
     </row>
-    <row r="181" spans="1:32">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A181" s="7"/>
       <c r="B181" s="49"/>
       <c r="C181" s="49"/>
@@ -23380,7 +23334,7 @@
       <c r="AE181" s="7"/>
       <c r="AF181" s="7"/>
     </row>
-    <row r="182" spans="1:32">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A182" s="7"/>
       <c r="B182" s="49"/>
       <c r="C182" s="49"/>
@@ -23414,7 +23368,7 @@
       <c r="AE182" s="7"/>
       <c r="AF182" s="7"/>
     </row>
-    <row r="183" spans="1:32">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A183" s="7"/>
       <c r="B183" s="49"/>
       <c r="C183" s="49"/>
@@ -23448,7 +23402,7 @@
       <c r="AE183" s="7"/>
       <c r="AF183" s="7"/>
     </row>
-    <row r="184" spans="1:32">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A184" s="7"/>
       <c r="B184" s="49"/>
       <c r="C184" s="49"/>
@@ -23482,7 +23436,7 @@
       <c r="AE184" s="7"/>
       <c r="AF184" s="7"/>
     </row>
-    <row r="185" spans="1:32">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A185" s="7"/>
       <c r="B185" s="49"/>
       <c r="C185" s="49"/>
@@ -23516,7 +23470,7 @@
       <c r="AE185" s="7"/>
       <c r="AF185" s="7"/>
     </row>
-    <row r="186" spans="1:32">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A186" s="7"/>
       <c r="B186" s="49"/>
       <c r="C186" s="49"/>
@@ -23550,7 +23504,7 @@
       <c r="AE186" s="7"/>
       <c r="AF186" s="7"/>
     </row>
-    <row r="187" spans="1:32">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A187" s="7"/>
       <c r="B187" s="49"/>
       <c r="C187" s="49"/>
@@ -23584,7 +23538,7 @@
       <c r="AE187" s="7"/>
       <c r="AF187" s="7"/>
     </row>
-    <row r="188" spans="1:32">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A188" s="7"/>
       <c r="B188" s="49"/>
       <c r="C188" s="49"/>
@@ -23618,7 +23572,7 @@
       <c r="AE188" s="7"/>
       <c r="AF188" s="7"/>
     </row>
-    <row r="189" spans="1:32">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A189" s="7"/>
       <c r="B189" s="49"/>
       <c r="C189" s="49"/>
@@ -23652,7 +23606,7 @@
       <c r="AE189" s="7"/>
       <c r="AF189" s="7"/>
     </row>
-    <row r="190" spans="1:32">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A190" s="7"/>
       <c r="B190" s="49"/>
       <c r="C190" s="49"/>
@@ -23686,7 +23640,7 @@
       <c r="AE190" s="7"/>
       <c r="AF190" s="7"/>
     </row>
-    <row r="191" spans="1:32">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A191" s="7"/>
       <c r="B191" s="49"/>
       <c r="C191" s="49"/>
@@ -23720,7 +23674,7 @@
       <c r="AE191" s="7"/>
       <c r="AF191" s="7"/>
     </row>
-    <row r="192" spans="1:32">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A192" s="7"/>
       <c r="B192" s="49"/>
       <c r="C192" s="49"/>
@@ -23754,7 +23708,7 @@
       <c r="AE192" s="7"/>
       <c r="AF192" s="7"/>
     </row>
-    <row r="193" spans="1:32">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A193" s="7"/>
       <c r="B193" s="49"/>
       <c r="C193" s="49"/>
@@ -23788,7 +23742,7 @@
       <c r="AE193" s="7"/>
       <c r="AF193" s="7"/>
     </row>
-    <row r="194" spans="1:32">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A194" s="7"/>
       <c r="B194" s="49"/>
       <c r="C194" s="49"/>
@@ -23822,7 +23776,7 @@
       <c r="AE194" s="7"/>
       <c r="AF194" s="7"/>
     </row>
-    <row r="195" spans="1:32">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A195" s="7"/>
       <c r="B195" s="49"/>
       <c r="C195" s="49"/>
@@ -23856,7 +23810,7 @@
       <c r="AE195" s="7"/>
       <c r="AF195" s="7"/>
     </row>
-    <row r="196" spans="1:32">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A196" s="7"/>
       <c r="B196" s="49"/>
       <c r="C196" s="49"/>
@@ -23890,7 +23844,7 @@
       <c r="AE196" s="7"/>
       <c r="AF196" s="7"/>
     </row>
-    <row r="197" spans="1:32">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A197" s="7"/>
       <c r="B197" s="49"/>
       <c r="C197" s="49"/>
@@ -23924,7 +23878,7 @@
       <c r="AE197" s="7"/>
       <c r="AF197" s="7"/>
     </row>
-    <row r="198" spans="1:32">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A198" s="7"/>
       <c r="B198" s="49"/>
       <c r="C198" s="49"/>
@@ -23958,7 +23912,7 @@
       <c r="AE198" s="7"/>
       <c r="AF198" s="7"/>
     </row>
-    <row r="199" spans="1:32">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A199" s="7"/>
       <c r="B199" s="49"/>
       <c r="C199" s="49"/>
@@ -23992,7 +23946,7 @@
       <c r="AE199" s="7"/>
       <c r="AF199" s="7"/>
     </row>
-    <row r="200" spans="1:32">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A200" s="7"/>
       <c r="B200" s="49"/>
       <c r="C200" s="49"/>
@@ -24026,7 +23980,7 @@
       <c r="AE200" s="7"/>
       <c r="AF200" s="7"/>
     </row>
-    <row r="201" spans="1:32">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A201" s="7"/>
       <c r="B201" s="49"/>
       <c r="C201" s="49"/>
@@ -24060,7 +24014,7 @@
       <c r="AE201" s="7"/>
       <c r="AF201" s="7"/>
     </row>
-    <row r="202" spans="1:32">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A202" s="7"/>
       <c r="B202" s="49"/>
       <c r="C202" s="49"/>
@@ -24094,7 +24048,7 @@
       <c r="AE202" s="7"/>
       <c r="AF202" s="7"/>
     </row>
-    <row r="203" spans="1:32">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A203" s="7"/>
       <c r="B203" s="49"/>
       <c r="C203" s="49"/>
@@ -24128,7 +24082,7 @@
       <c r="AE203" s="7"/>
       <c r="AF203" s="7"/>
     </row>
-    <row r="204" spans="1:32">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A204" s="7"/>
       <c r="B204" s="49"/>
       <c r="C204" s="49"/>
@@ -24162,7 +24116,7 @@
       <c r="AE204" s="7"/>
       <c r="AF204" s="7"/>
     </row>
-    <row r="205" spans="1:32">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A205" s="7"/>
       <c r="B205" s="49"/>
       <c r="C205" s="49"/>
@@ -24196,7 +24150,7 @@
       <c r="AE205" s="7"/>
       <c r="AF205" s="7"/>
     </row>
-    <row r="206" spans="1:32">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A206" s="7"/>
       <c r="B206" s="49"/>
       <c r="C206" s="49"/>
@@ -24230,7 +24184,7 @@
       <c r="AE206" s="7"/>
       <c r="AF206" s="7"/>
     </row>
-    <row r="207" spans="1:32">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A207" s="7"/>
       <c r="B207" s="49"/>
       <c r="C207" s="49"/>
@@ -24264,7 +24218,7 @@
       <c r="AE207" s="7"/>
       <c r="AF207" s="7"/>
     </row>
-    <row r="208" spans="1:32">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A208" s="7"/>
       <c r="B208" s="49"/>
       <c r="C208" s="49"/>
@@ -24298,7 +24252,7 @@
       <c r="AE208" s="7"/>
       <c r="AF208" s="7"/>
     </row>
-    <row r="209" spans="1:32">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A209" s="7"/>
       <c r="B209" s="49"/>
       <c r="C209" s="49"/>
@@ -24332,7 +24286,7 @@
       <c r="AE209" s="7"/>
       <c r="AF209" s="7"/>
     </row>
-    <row r="210" spans="1:32">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A210" s="7"/>
       <c r="B210" s="49"/>
       <c r="C210" s="49"/>
@@ -24366,7 +24320,7 @@
       <c r="AE210" s="7"/>
       <c r="AF210" s="7"/>
     </row>
-    <row r="211" spans="1:32">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A211" s="7"/>
       <c r="B211" s="49"/>
       <c r="C211" s="49"/>
@@ -24400,7 +24354,7 @@
       <c r="AE211" s="7"/>
       <c r="AF211" s="7"/>
     </row>
-    <row r="212" spans="1:32">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A212" s="7"/>
       <c r="B212" s="49"/>
       <c r="C212" s="49"/>
@@ -24434,7 +24388,7 @@
       <c r="AE212" s="7"/>
       <c r="AF212" s="7"/>
     </row>
-    <row r="213" spans="1:32">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A213" s="7"/>
       <c r="B213" s="49"/>
       <c r="C213" s="49"/>
@@ -24468,7 +24422,7 @@
       <c r="AE213" s="7"/>
       <c r="AF213" s="7"/>
     </row>
-    <row r="214" spans="1:32">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A214" s="7"/>
       <c r="B214" s="49"/>
       <c r="C214" s="49"/>
@@ -24502,7 +24456,7 @@
       <c r="AE214" s="7"/>
       <c r="AF214" s="7"/>
     </row>
-    <row r="215" spans="1:32">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A215" s="7"/>
       <c r="B215" s="49"/>
       <c r="C215" s="49"/>
@@ -24536,7 +24490,7 @@
       <c r="AE215" s="7"/>
       <c r="AF215" s="7"/>
     </row>
-    <row r="216" spans="1:32">
+    <row r="216" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A216" s="7"/>
       <c r="B216" s="49"/>
       <c r="C216" s="49"/>
@@ -24570,7 +24524,7 @@
       <c r="AE216" s="7"/>
       <c r="AF216" s="7"/>
     </row>
-    <row r="217" spans="1:32">
+    <row r="217" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A217" s="7"/>
       <c r="B217" s="49"/>
       <c r="C217" s="49"/>
@@ -24604,7 +24558,7 @@
       <c r="AE217" s="7"/>
       <c r="AF217" s="7"/>
     </row>
-    <row r="218" spans="1:32">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A218" s="7"/>
       <c r="B218" s="49"/>
       <c r="C218" s="49"/>
@@ -24638,7 +24592,7 @@
       <c r="AE218" s="7"/>
       <c r="AF218" s="7"/>
     </row>
-    <row r="219" spans="1:32">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A219" s="7"/>
       <c r="B219" s="49"/>
       <c r="C219" s="49"/>
@@ -24672,7 +24626,7 @@
       <c r="AE219" s="7"/>
       <c r="AF219" s="7"/>
     </row>
-    <row r="220" spans="1:32">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A220" s="7"/>
       <c r="B220" s="49"/>
       <c r="C220" s="49"/>
@@ -24706,7 +24660,7 @@
       <c r="AE220" s="7"/>
       <c r="AF220" s="7"/>
     </row>
-    <row r="221" spans="1:32">
+    <row r="221" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A221" s="7"/>
       <c r="B221" s="49"/>
       <c r="C221" s="49"/>
@@ -24740,7 +24694,7 @@
       <c r="AE221" s="7"/>
       <c r="AF221" s="7"/>
     </row>
-    <row r="222" spans="1:32">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A222" s="7"/>
       <c r="B222" s="49"/>
       <c r="C222" s="49"/>
@@ -24774,7 +24728,7 @@
       <c r="AE222" s="7"/>
       <c r="AF222" s="7"/>
     </row>
-    <row r="223" spans="1:32">
+    <row r="223" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A223" s="7"/>
       <c r="B223" s="49"/>
       <c r="C223" s="49"/>
@@ -24808,7 +24762,7 @@
       <c r="AE223" s="7"/>
       <c r="AF223" s="7"/>
     </row>
-    <row r="224" spans="1:32">
+    <row r="224" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A224" s="7"/>
       <c r="B224" s="49"/>
       <c r="C224" s="49"/>
@@ -24842,7 +24796,7 @@
       <c r="AE224" s="7"/>
       <c r="AF224" s="7"/>
     </row>
-    <row r="225" spans="1:32">
+    <row r="225" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A225" s="7"/>
       <c r="B225" s="49"/>
       <c r="C225" s="49"/>
@@ -24876,7 +24830,7 @@
       <c r="AE225" s="7"/>
       <c r="AF225" s="7"/>
     </row>
-    <row r="226" spans="1:32">
+    <row r="226" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A226" s="7"/>
       <c r="B226" s="49"/>
       <c r="C226" s="49"/>
@@ -24910,7 +24864,7 @@
       <c r="AE226" s="7"/>
       <c r="AF226" s="7"/>
     </row>
-    <row r="227" spans="1:32">
+    <row r="227" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A227" s="7"/>
       <c r="B227" s="49"/>
       <c r="C227" s="49"/>
@@ -24944,7 +24898,7 @@
       <c r="AE227" s="7"/>
       <c r="AF227" s="7"/>
     </row>
-    <row r="228" spans="1:32">
+    <row r="228" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A228" s="7"/>
       <c r="B228" s="49"/>
       <c r="C228" s="49"/>
@@ -24978,7 +24932,7 @@
       <c r="AE228" s="7"/>
       <c r="AF228" s="7"/>
     </row>
-    <row r="229" spans="1:32">
+    <row r="229" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A229" s="7"/>
       <c r="B229" s="49"/>
       <c r="C229" s="49"/>
@@ -25012,7 +24966,7 @@
       <c r="AE229" s="7"/>
       <c r="AF229" s="7"/>
     </row>
-    <row r="230" spans="1:32">
+    <row r="230" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A230" s="7"/>
       <c r="B230" s="7"/>
       <c r="C230" s="7"/>
@@ -25046,7 +25000,7 @@
       <c r="AE230" s="7"/>
       <c r="AF230" s="7"/>
     </row>
-    <row r="231" spans="1:32">
+    <row r="231" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A231" s="7"/>
       <c r="B231" s="7"/>
       <c r="C231" s="7"/>
@@ -25080,7 +25034,7 @@
       <c r="AE231" s="7"/>
       <c r="AF231" s="7"/>
     </row>
-    <row r="232" spans="1:32">
+    <row r="232" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A232" s="7"/>
       <c r="B232" s="7"/>
       <c r="C232" s="7"/>
@@ -25114,7 +25068,7 @@
       <c r="AE232" s="7"/>
       <c r="AF232" s="7"/>
     </row>
-    <row r="233" spans="1:32">
+    <row r="233" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A233" s="7"/>
       <c r="B233" s="7"/>
       <c r="C233" s="7"/>
@@ -25150,21 +25104,27 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="I2:Q4"/>
+    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B8:F10"/>
+    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="L14:Q14"/>
     <mergeCell ref="L15:Q15"/>
@@ -25181,27 +25141,21 @@
     <mergeCell ref="I17:Q17"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="I2:Q4"/>
-    <mergeCell ref="I5:Q5"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B8:F10"/>
-    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
